--- a/9_Hisui_Data.xlsx
+++ b/9_Hisui_Data.xlsx
@@ -399,20 +399,1256 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:A2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Route</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:E72"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Challenge Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Requisite</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Reward Map</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Reward Challenge</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Reward Gift</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Challenge 3</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Horseshoe Plains</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Challenge 4</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Deertrack Path</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Challenge 5</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Deertrack Heights</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Challenge 6</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Gym - Kleavor, Droning Meadow, Grueling Grove</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Challenge 7</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Earn Kleavor Badge</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Oreburrow Tunnel</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Challenge 8</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Nature’s Pantry</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Challenge 9</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C8" t="str">
+        <v>The Heartwood North</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Challenge 10</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C9" t="str">
+        <v>The Heartwood South</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Challenge 11</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Golden Lowlands North</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Challenge 12</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Golden Lowlands South</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Challenge 13</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Gapejaw Bog North</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Challenge 14</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Gapejaw Bog South</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Challenge 15</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Gym - Lilligant, Obsidian Falls</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Challenge 16</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Earn Lilligant Badge</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Ursa's Ring</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Challenge 17</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Sludge Mound</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Challenge 18</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Scarlet Bog</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Challenge 19</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Bolderoll Slope</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Challenge 20</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Holm of Trials</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Challenge 21</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Crossing Slope</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Challenge 22</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Bathers' Lagoon</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Challenge 23</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Castaway Shore</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Challenge 24</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Deadwood Haunt</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Challenge 25</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Gym - Arcanine</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Challenge 26</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Earn Arcanine Badge</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Veilstone Cape, Gym - Warden Ingo</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Challenge 27</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Tranquility Cove</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Challenge 28</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Islespy Shore</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Challenge 29</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Firespit Island</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Challenge 30</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Spring Path</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Challenge 31</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Celestica Trail</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Challenge 32</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Celestica Ruins</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Challenge 33</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Sacred Plaza</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Challenge 34</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Stonetooth Rows</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Challenge 35</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Primeval Grotto</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Challenge 36</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Gym - Electrode</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Challenge 37</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Earn Electrode Badge</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Clamberclaw Cliffs, Coronet Highlands Fishing Spot</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Challenge 38</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Coronet Highlands</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Challenge 39</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Fabled Spring</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Challenge 40</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Whiteout Valley</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Challenge 41</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Bonechill Wastes North</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Challenge 42</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Bonechill Wastes South</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Challenge 43</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Arena's Approach</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Challenge 44</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Glacier Terrace</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Challenge 45</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Heart's Crag</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Challenge 46</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Snowpoint Temple</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Challenge 47</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Gym - Avalugg</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Extra Challenge A 1</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Earn Warden Ingo Badge</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Obsidian Fieldlands Fishing Spot</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Extra Challenge A 2</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Cobalt Coastlands Fishing Spot</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Extra Challenge A 3</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Crimson Mirelands Fishing Spot</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Extra Challenge A 4</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Ginkgo Landing</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Extra Challenge A 5</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Shrouded Ruins</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Extra Challenge A 6</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Sandgem Flats South</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Extra Challenge A 7</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Ramanas Island South</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Extra Challenge A 8</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Sandgem Flats North</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Extra Challenge B 1</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Cloudpool Ridge North</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Extra Challenge B 2</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Cloudpool Ridge South</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Extra Challenge B 3</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Space-Time Distortion</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Extra Challenge C 1</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Seagrass Haven</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Extra Challenge C 2</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Moonview Arena</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Extra Challenge D 1</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Worn Bridge</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Extra Challenge D 2</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Incarnate Fields</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Extra Challenge E 1</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Lake Valor</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Extra Challenge E 2</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Lake of Trials</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Extra Challenge F 1</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Defeat 10 in undefined</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Gym of Etertime</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Challenge 48</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Earn Avalugg Badge</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Etertime Storm, Wayward Cave, Alabaster Icelands Fishing Spot, Lake Verity, Etertime Storm</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Extra Challenge B 4</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Catch Species: undefined xundefined, undefined xundefined, undefined xundefined, undefined xundefined, undefined xundefined</v>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Extra Challenge C 3</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Catch Species: undefined xundefined, undefined xundefined, undefined xundefined</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Extra Challenge D 3</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Catch Species: undefined xundefined, undefined xundefined, undefined xundefined, undefined xundefined</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Extra Challenge E 3</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Catch Species: undefined xundefined, undefined xundefined, undefined xundefined</v>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Extra Challenge F 2</v>
+      </c>
+      <c r="B70" t="str">
+        <v>{"defeatMultipleSpecific":[{"name":"Adam"},{"name":"Irida"}]}</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Key to Etertime Citadel</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Complete Extra Challenge C 3, Extra Challenge D 3, Extra Challenge E 3, Extra Challenge F 2</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Etertime Citadel</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Etertime Citadel</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Catch Species: undefined xundefined, undefined xundefined, undefined xundefined, undefined xundefined</v>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E72"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/9_Hisui_Data.xlsx
+++ b/9_Hisui_Data.xlsx
@@ -1080,7 +1080,7 @@
         <v>10-12</v>
       </c>
       <c r="G15" t="str">
-        <v>3-5</v>
+        <v>2-4</v>
       </c>
       <c r="H15" s="1">
         <v>0.14</v>
@@ -1127,7 +1127,7 @@
         <v>10-12</v>
       </c>
       <c r="G16" t="str">
-        <v>3-5</v>
+        <v>2-4</v>
       </c>
       <c r="H16" s="1">
         <v>0.14</v>
@@ -1174,7 +1174,7 @@
         <v>10-12</v>
       </c>
       <c r="G17" t="str">
-        <v>3-5</v>
+        <v>2-4</v>
       </c>
       <c r="H17" s="1">
         <v>0.14</v>
@@ -1221,7 +1221,7 @@
         <v>10-12</v>
       </c>
       <c r="G18" t="str">
-        <v>3-5</v>
+        <v>2-4</v>
       </c>
       <c r="H18" s="1">
         <v>0.14</v>
@@ -1268,7 +1268,7 @@
         <v>10-12</v>
       </c>
       <c r="G19" t="str">
-        <v>3-5</v>
+        <v>2-4</v>
       </c>
       <c r="H19" s="1">
         <v>0.14</v>
@@ -1315,7 +1315,7 @@
         <v>10-12</v>
       </c>
       <c r="G20" t="str">
-        <v>3-5</v>
+        <v>2-4</v>
       </c>
       <c r="H20" s="1">
         <v>0.14</v>
@@ -1362,7 +1362,7 @@
         <v>10-12</v>
       </c>
       <c r="G21" t="str">
-        <v>3-5</v>
+        <v>2-4</v>
       </c>
       <c r="H21" s="1">
         <v>0.16</v>
@@ -1456,7 +1456,7 @@
         <v>11-13</v>
       </c>
       <c r="G23" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H23" s="1">
         <v>0.16</v>
@@ -1503,7 +1503,7 @@
         <v>11-13</v>
       </c>
       <c r="G24" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H24" s="1">
         <v>0.16</v>
@@ -1550,7 +1550,7 @@
         <v>11-13</v>
       </c>
       <c r="G25" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H25" s="1">
         <v>0.16</v>
@@ -1597,7 +1597,7 @@
         <v>11-13</v>
       </c>
       <c r="G26" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H26" s="1">
         <v>0.16</v>
@@ -1644,7 +1644,7 @@
         <v>11-13</v>
       </c>
       <c r="G27" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H27" s="1">
         <v>0.16</v>
@@ -1691,7 +1691,7 @@
         <v>11-13</v>
       </c>
       <c r="G28" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H28" s="1">
         <v>0.2</v>
@@ -1738,7 +1738,7 @@
         <v>11-13</v>
       </c>
       <c r="G29" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H29" s="1">
         <v>0.2</v>
@@ -1785,7 +1785,7 @@
         <v>11-13</v>
       </c>
       <c r="G30" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H30" s="1">
         <v>0.2</v>
@@ -1832,7 +1832,7 @@
         <v>11-13</v>
       </c>
       <c r="G31" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H31" s="1">
         <v>0.2</v>
@@ -1879,7 +1879,7 @@
         <v>11-13</v>
       </c>
       <c r="G32" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H32" s="1">
         <v>0.2</v>
@@ -1926,7 +1926,7 @@
         <v>11-13</v>
       </c>
       <c r="G33" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H33" s="1">
         <v>0.2</v>
@@ -2584,7 +2584,7 @@
         <v>15-17</v>
       </c>
       <c r="G47" t="str">
-        <v>10-12</v>
+        <v>9-11</v>
       </c>
       <c r="H47" s="1">
         <v>0.14</v>
@@ -2631,7 +2631,7 @@
         <v>15-17</v>
       </c>
       <c r="G48" t="str">
-        <v>10-12</v>
+        <v>9-11</v>
       </c>
       <c r="H48" s="1">
         <v>0.14</v>
@@ -2678,7 +2678,7 @@
         <v>15-17</v>
       </c>
       <c r="G49" t="str">
-        <v>10-12</v>
+        <v>9-11</v>
       </c>
       <c r="H49" s="1">
         <v>0.14</v>
@@ -2725,7 +2725,7 @@
         <v>15-17</v>
       </c>
       <c r="G50" t="str">
-        <v>10-12</v>
+        <v>9-11</v>
       </c>
       <c r="H50" s="1">
         <v>0.14</v>
@@ -2772,7 +2772,7 @@
         <v>15-17</v>
       </c>
       <c r="G51" t="str">
-        <v>10-12</v>
+        <v>9-11</v>
       </c>
       <c r="H51" s="1">
         <v>0.14</v>
@@ -2819,7 +2819,7 @@
         <v>15-17</v>
       </c>
       <c r="G52" t="str">
-        <v>10-12</v>
+        <v>9-11</v>
       </c>
       <c r="H52" s="1">
         <v>0.14</v>
@@ -2866,7 +2866,7 @@
         <v>15-17</v>
       </c>
       <c r="G53" t="str">
-        <v>10-12</v>
+        <v>9-11</v>
       </c>
       <c r="H53" s="1">
         <v>0.16</v>
@@ -2913,7 +2913,7 @@
         <v>16-18</v>
       </c>
       <c r="G54" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H54" s="1">
         <v>0.2</v>
@@ -2960,7 +2960,7 @@
         <v>16-18</v>
       </c>
       <c r="G55" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H55" s="1">
         <v>0.2</v>
@@ -3007,7 +3007,7 @@
         <v>16-18</v>
       </c>
       <c r="G56" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H56" s="1">
         <v>0.2</v>
@@ -3054,7 +3054,7 @@
         <v>16-18</v>
       </c>
       <c r="G57" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H57" s="1">
         <v>0.2</v>
@@ -3101,7 +3101,7 @@
         <v>16-18</v>
       </c>
       <c r="G58" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H58" s="1">
         <v>0.2</v>
@@ -3430,7 +3430,7 @@
         <v>21-23</v>
       </c>
       <c r="G65" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H65" s="1">
         <v>0.16</v>
@@ -3477,7 +3477,7 @@
         <v>21-23</v>
       </c>
       <c r="G66" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H66" s="1">
         <v>0.16</v>
@@ -3524,7 +3524,7 @@
         <v>21-23</v>
       </c>
       <c r="G67" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H67" s="1">
         <v>0.16</v>
@@ -3571,7 +3571,7 @@
         <v>21-23</v>
       </c>
       <c r="G68" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H68" s="1">
         <v>0.16</v>
@@ -3618,7 +3618,7 @@
         <v>21-23</v>
       </c>
       <c r="G69" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H69" s="1">
         <v>0.16</v>
@@ -3665,7 +3665,7 @@
         <v>21-23</v>
       </c>
       <c r="G70" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H70" s="1">
         <v>0.2</v>
@@ -3712,7 +3712,7 @@
         <v>23-25</v>
       </c>
       <c r="G71" t="str">
-        <v>19-22</v>
+        <v>18-21</v>
       </c>
       <c r="H71" s="1">
         <v>0.33</v>
@@ -3759,7 +3759,7 @@
         <v>23-25</v>
       </c>
       <c r="G72" t="str">
-        <v>19-22</v>
+        <v>18-21</v>
       </c>
       <c r="H72" s="1">
         <v>0.33</v>
@@ -3806,7 +3806,7 @@
         <v>23-25</v>
       </c>
       <c r="G73" t="str">
-        <v>19-22</v>
+        <v>18-21</v>
       </c>
       <c r="H73" s="1">
         <v>0.34</v>
@@ -4511,7 +4511,7 @@
         <v>27-29</v>
       </c>
       <c r="G88" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H88" s="1">
         <v>0.16</v>
@@ -4558,7 +4558,7 @@
         <v>27-29</v>
       </c>
       <c r="G89" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H89" s="1">
         <v>0.16</v>
@@ -4605,7 +4605,7 @@
         <v>27-29</v>
       </c>
       <c r="G90" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H90" s="1">
         <v>0.16</v>
@@ -4652,7 +4652,7 @@
         <v>27-29</v>
       </c>
       <c r="G91" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H91" s="1">
         <v>0.16</v>
@@ -4699,7 +4699,7 @@
         <v>27-29</v>
       </c>
       <c r="G92" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H92" s="1">
         <v>0.16</v>
@@ -4746,7 +4746,7 @@
         <v>27-29</v>
       </c>
       <c r="G93" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H93" s="1">
         <v>0.2</v>
@@ -4793,7 +4793,7 @@
         <v>28-30</v>
       </c>
       <c r="G94" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H94" s="1">
         <v>0.33</v>
@@ -4840,7 +4840,7 @@
         <v>28-30</v>
       </c>
       <c r="G95" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H95" s="1">
         <v>0.33</v>
@@ -4887,7 +4887,7 @@
         <v>28-30</v>
       </c>
       <c r="G96" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H96" s="1">
         <v>0.34</v>
@@ -5263,7 +5263,7 @@
         <v>33-35</v>
       </c>
       <c r="G104" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H104" s="1">
         <v>0.14</v>
@@ -5310,7 +5310,7 @@
         <v>33-35</v>
       </c>
       <c r="G105" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H105" s="1">
         <v>0.14</v>
@@ -5357,7 +5357,7 @@
         <v>33-35</v>
       </c>
       <c r="G106" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H106" s="1">
         <v>0.14</v>
@@ -5404,7 +5404,7 @@
         <v>33-35</v>
       </c>
       <c r="G107" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H107" s="1">
         <v>0.14</v>
@@ -5451,7 +5451,7 @@
         <v>33-35</v>
       </c>
       <c r="G108" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H108" s="1">
         <v>0.14</v>
@@ -5498,7 +5498,7 @@
         <v>33-35</v>
       </c>
       <c r="G109" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H109" s="1">
         <v>0.14</v>
@@ -5545,7 +5545,7 @@
         <v>33-35</v>
       </c>
       <c r="G110" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H110" s="1">
         <v>0.16</v>
@@ -5592,7 +5592,7 @@
         <v>35-37</v>
       </c>
       <c r="G111" t="str">
-        <v>33-37</v>
+        <v>32-35</v>
       </c>
       <c r="H111" s="1">
         <v>0.25</v>
@@ -5639,7 +5639,7 @@
         <v>35-37</v>
       </c>
       <c r="G112" t="str">
-        <v>33-37</v>
+        <v>32-35</v>
       </c>
       <c r="H112" s="1">
         <v>0.25</v>
@@ -5686,7 +5686,7 @@
         <v>35-37</v>
       </c>
       <c r="G113" t="str">
-        <v>33-37</v>
+        <v>32-35</v>
       </c>
       <c r="H113" s="1">
         <v>0.25</v>
@@ -5733,7 +5733,7 @@
         <v>35-37</v>
       </c>
       <c r="G114" t="str">
-        <v>33-37</v>
+        <v>32-35</v>
       </c>
       <c r="H114" s="1">
         <v>0.25</v>
@@ -5780,7 +5780,7 @@
         <v>37-39</v>
       </c>
       <c r="G115" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H115" s="1">
         <v>0.33</v>
@@ -5827,7 +5827,7 @@
         <v>37-39</v>
       </c>
       <c r="G116" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H116" s="1">
         <v>0.33</v>
@@ -5874,7 +5874,7 @@
         <v>37-39</v>
       </c>
       <c r="G117" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H117" s="1">
         <v>0.34</v>
@@ -5921,7 +5921,7 @@
         <v>39-41</v>
       </c>
       <c r="G118" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H118" s="1">
         <v>0.25</v>
@@ -5968,7 +5968,7 @@
         <v>39-41</v>
       </c>
       <c r="G119" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H119" s="1">
         <v>0.25</v>
@@ -6015,7 +6015,7 @@
         <v>39-41</v>
       </c>
       <c r="G120" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H120" s="1">
         <v>0.25</v>
@@ -6062,7 +6062,7 @@
         <v>39-41</v>
       </c>
       <c r="G121" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H121" s="1">
         <v>0.25</v>
@@ -6156,7 +6156,7 @@
         <v>40-42</v>
       </c>
       <c r="G123" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H123" s="1">
         <v>0.2</v>
@@ -6203,7 +6203,7 @@
         <v>40-42</v>
       </c>
       <c r="G124" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H124" s="1">
         <v>0.2</v>
@@ -6250,7 +6250,7 @@
         <v>40-42</v>
       </c>
       <c r="G125" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H125" s="1">
         <v>0.2</v>
@@ -6297,7 +6297,7 @@
         <v>40-42</v>
       </c>
       <c r="G126" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H126" s="1">
         <v>0.2</v>
@@ -6344,7 +6344,7 @@
         <v>40-42</v>
       </c>
       <c r="G127" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H127" s="1">
         <v>0.2</v>
@@ -6391,7 +6391,7 @@
         <v>42-44</v>
       </c>
       <c r="G128" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H128" s="1">
         <v>0.2</v>
@@ -6438,7 +6438,7 @@
         <v>42-44</v>
       </c>
       <c r="G129" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H129" s="1">
         <v>0.2</v>
@@ -6485,7 +6485,7 @@
         <v>42-44</v>
       </c>
       <c r="G130" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H130" s="1">
         <v>0.2</v>
@@ -6532,7 +6532,7 @@
         <v>42-44</v>
       </c>
       <c r="G131" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H131" s="1">
         <v>0.2</v>
@@ -6579,7 +6579,7 @@
         <v>42-44</v>
       </c>
       <c r="G132" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H132" s="1">
         <v>0.2</v>
@@ -6626,7 +6626,7 @@
         <v>44-46</v>
       </c>
       <c r="G133" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H133" s="1">
         <v>0.16</v>
@@ -6673,7 +6673,7 @@
         <v>44-46</v>
       </c>
       <c r="G134" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H134" s="1">
         <v>0.16</v>
@@ -6720,7 +6720,7 @@
         <v>44-46</v>
       </c>
       <c r="G135" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H135" s="1">
         <v>0.16</v>
@@ -6767,7 +6767,7 @@
         <v>44-46</v>
       </c>
       <c r="G136" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H136" s="1">
         <v>0.16</v>
@@ -6814,7 +6814,7 @@
         <v>44-46</v>
       </c>
       <c r="G137" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H137" s="1">
         <v>0.16</v>
@@ -6861,7 +6861,7 @@
         <v>44-46</v>
       </c>
       <c r="G138" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H138" s="1">
         <v>0.2</v>
@@ -6908,7 +6908,7 @@
         <v>45-47</v>
       </c>
       <c r="G139" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H139" s="1">
         <v>0.2</v>
@@ -6955,7 +6955,7 @@
         <v>45-47</v>
       </c>
       <c r="G140" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H140" s="1">
         <v>0.2</v>
@@ -7002,7 +7002,7 @@
         <v>45-47</v>
       </c>
       <c r="G141" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H141" s="1">
         <v>0.2</v>
@@ -7049,7 +7049,7 @@
         <v>45-47</v>
       </c>
       <c r="G142" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H142" s="1">
         <v>0.2</v>
@@ -7096,7 +7096,7 @@
         <v>45-47</v>
       </c>
       <c r="G143" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H143" s="1">
         <v>0.2</v>
@@ -7143,7 +7143,7 @@
         <v>47-49</v>
       </c>
       <c r="G144" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H144" s="1">
         <v>0.25</v>
@@ -7190,7 +7190,7 @@
         <v>47-49</v>
       </c>
       <c r="G145" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H145" s="1">
         <v>0.25</v>
@@ -7237,7 +7237,7 @@
         <v>47-49</v>
       </c>
       <c r="G146" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H146" s="1">
         <v>0.25</v>
@@ -7284,7 +7284,7 @@
         <v>47-49</v>
       </c>
       <c r="G147" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H147" s="1">
         <v>0.25</v>
@@ -7331,7 +7331,7 @@
         <v>49-51</v>
       </c>
       <c r="G148" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H148" s="1">
         <v>0.2</v>
@@ -7378,7 +7378,7 @@
         <v>49-51</v>
       </c>
       <c r="G149" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H149" s="1">
         <v>0.2</v>
@@ -7425,7 +7425,7 @@
         <v>49-51</v>
       </c>
       <c r="G150" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H150" s="1">
         <v>0.2</v>
@@ -7472,7 +7472,7 @@
         <v>49-51</v>
       </c>
       <c r="G151" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H151" s="1">
         <v>0.2</v>
@@ -7519,7 +7519,7 @@
         <v>49-51</v>
       </c>
       <c r="G152" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H152" s="1">
         <v>0.2</v>
@@ -7566,7 +7566,7 @@
         <v>50-52</v>
       </c>
       <c r="G153" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H153" s="1">
         <v>0.25</v>
@@ -7613,7 +7613,7 @@
         <v>50-52</v>
       </c>
       <c r="G154" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H154" s="1">
         <v>0.25</v>
@@ -7660,7 +7660,7 @@
         <v>50-52</v>
       </c>
       <c r="G155" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H155" s="1">
         <v>0.25</v>
@@ -7707,7 +7707,7 @@
         <v>50-52</v>
       </c>
       <c r="G156" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H156" s="1">
         <v>0.25</v>
@@ -7754,7 +7754,7 @@
         <v>52-54</v>
       </c>
       <c r="G157" t="str">
-        <v>52-58</v>
+        <v>51-56</v>
       </c>
       <c r="H157" s="1">
         <v>0.2</v>
@@ -7801,7 +7801,7 @@
         <v>52-54</v>
       </c>
       <c r="G158" t="str">
-        <v>52-58</v>
+        <v>51-56</v>
       </c>
       <c r="H158" s="1">
         <v>0.2</v>
@@ -7848,7 +7848,7 @@
         <v>52-54</v>
       </c>
       <c r="G159" t="str">
-        <v>52-58</v>
+        <v>51-56</v>
       </c>
       <c r="H159" s="1">
         <v>0.2</v>
@@ -7895,7 +7895,7 @@
         <v>52-54</v>
       </c>
       <c r="G160" t="str">
-        <v>52-58</v>
+        <v>51-56</v>
       </c>
       <c r="H160" s="1">
         <v>0.2</v>
@@ -7942,7 +7942,7 @@
         <v>52-54</v>
       </c>
       <c r="G161" t="str">
-        <v>52-58</v>
+        <v>51-56</v>
       </c>
       <c r="H161" s="1">
         <v>0.2</v>
@@ -7989,7 +7989,7 @@
         <v>54-56</v>
       </c>
       <c r="G162" t="str">
-        <v>53-59</v>
+        <v>53-58</v>
       </c>
       <c r="H162" s="1">
         <v>0.2</v>
@@ -8036,7 +8036,7 @@
         <v>54-56</v>
       </c>
       <c r="G163" t="str">
-        <v>53-59</v>
+        <v>53-58</v>
       </c>
       <c r="H163" s="1">
         <v>0.2</v>
@@ -8083,7 +8083,7 @@
         <v>54-56</v>
       </c>
       <c r="G164" t="str">
-        <v>53-59</v>
+        <v>53-58</v>
       </c>
       <c r="H164" s="1">
         <v>0.2</v>
@@ -8130,7 +8130,7 @@
         <v>54-56</v>
       </c>
       <c r="G165" t="str">
-        <v>53-59</v>
+        <v>53-58</v>
       </c>
       <c r="H165" s="1">
         <v>0.2</v>
@@ -8177,7 +8177,7 @@
         <v>54-56</v>
       </c>
       <c r="G166" t="str">
-        <v>53-59</v>
+        <v>53-58</v>
       </c>
       <c r="H166" s="1">
         <v>0.2</v>
@@ -8224,7 +8224,7 @@
         <v>56-58</v>
       </c>
       <c r="G167" t="str">
-        <v>55-61</v>
+        <v>55-60</v>
       </c>
       <c r="H167" s="1">
         <v>0.16</v>
@@ -8271,7 +8271,7 @@
         <v>56-58</v>
       </c>
       <c r="G168" t="str">
-        <v>55-61</v>
+        <v>55-60</v>
       </c>
       <c r="H168" s="1">
         <v>0.16</v>
@@ -8318,7 +8318,7 @@
         <v>56-58</v>
       </c>
       <c r="G169" t="str">
-        <v>55-61</v>
+        <v>55-60</v>
       </c>
       <c r="H169" s="1">
         <v>0.16</v>
@@ -8365,7 +8365,7 @@
         <v>56-58</v>
       </c>
       <c r="G170" t="str">
-        <v>55-61</v>
+        <v>55-60</v>
       </c>
       <c r="H170" s="1">
         <v>0.16</v>
@@ -8412,7 +8412,7 @@
         <v>56-58</v>
       </c>
       <c r="G171" t="str">
-        <v>55-61</v>
+        <v>55-60</v>
       </c>
       <c r="H171" s="1">
         <v>0.16</v>
@@ -8459,7 +8459,7 @@
         <v>56-58</v>
       </c>
       <c r="G172" t="str">
-        <v>55-61</v>
+        <v>55-60</v>
       </c>
       <c r="H172" s="1">
         <v>0.2</v>
@@ -8553,7 +8553,7 @@
         <v>57-59</v>
       </c>
       <c r="G174" t="str">
-        <v>59-65</v>
+        <v>58-63</v>
       </c>
       <c r="H174" s="1">
         <v>0.25</v>
@@ -8600,7 +8600,7 @@
         <v>57-59</v>
       </c>
       <c r="G175" t="str">
-        <v>59-65</v>
+        <v>58-63</v>
       </c>
       <c r="H175" s="1">
         <v>0.25</v>
@@ -8647,7 +8647,7 @@
         <v>57-59</v>
       </c>
       <c r="G176" t="str">
-        <v>59-65</v>
+        <v>58-63</v>
       </c>
       <c r="H176" s="1">
         <v>0.25</v>
@@ -8694,7 +8694,7 @@
         <v>57-59</v>
       </c>
       <c r="G177" t="str">
-        <v>59-65</v>
+        <v>58-63</v>
       </c>
       <c r="H177" s="1">
         <v>0.25</v>
@@ -8741,7 +8741,7 @@
         <v>59-61</v>
       </c>
       <c r="G178" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H178" s="1">
         <v>0.33</v>
@@ -8788,7 +8788,7 @@
         <v>59-61</v>
       </c>
       <c r="G179" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H179" s="1">
         <v>0.33</v>
@@ -8835,7 +8835,7 @@
         <v>59-61</v>
       </c>
       <c r="G180" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H180" s="1">
         <v>0.34</v>
@@ -8882,7 +8882,7 @@
         <v>61-63</v>
       </c>
       <c r="G181" t="str">
-        <v>62-69</v>
+        <v>62-68</v>
       </c>
       <c r="H181" s="1">
         <v>0.25</v>
@@ -8929,7 +8929,7 @@
         <v>61-63</v>
       </c>
       <c r="G182" t="str">
-        <v>62-69</v>
+        <v>62-68</v>
       </c>
       <c r="H182" s="1">
         <v>0.25</v>
@@ -8976,7 +8976,7 @@
         <v>61-63</v>
       </c>
       <c r="G183" t="str">
-        <v>62-69</v>
+        <v>62-68</v>
       </c>
       <c r="H183" s="1">
         <v>0.25</v>
@@ -9023,7 +9023,7 @@
         <v>61-63</v>
       </c>
       <c r="G184" t="str">
-        <v>62-69</v>
+        <v>62-68</v>
       </c>
       <c r="H184" s="1">
         <v>0.25</v>
@@ -9070,7 +9070,7 @@
         <v>62-64</v>
       </c>
       <c r="G185" t="str">
-        <v>64-71</v>
+        <v>64-70</v>
       </c>
       <c r="H185" s="1">
         <v>0.33</v>
@@ -9117,7 +9117,7 @@
         <v>62-64</v>
       </c>
       <c r="G186" t="str">
-        <v>64-71</v>
+        <v>64-70</v>
       </c>
       <c r="H186" s="1">
         <v>0.33</v>
@@ -9164,7 +9164,7 @@
         <v>62-64</v>
       </c>
       <c r="G187" t="str">
-        <v>64-71</v>
+        <v>64-70</v>
       </c>
       <c r="H187" s="1">
         <v>0.34</v>
@@ -9211,7 +9211,7 @@
         <v>64-66</v>
       </c>
       <c r="G188" t="str">
-        <v>66-73</v>
+        <v>65-71</v>
       </c>
       <c r="H188" s="1">
         <v>0.25</v>
@@ -9258,7 +9258,7 @@
         <v>64-66</v>
       </c>
       <c r="G189" t="str">
-        <v>66-73</v>
+        <v>65-71</v>
       </c>
       <c r="H189" s="1">
         <v>0.25</v>
@@ -9305,7 +9305,7 @@
         <v>64-66</v>
       </c>
       <c r="G190" t="str">
-        <v>66-73</v>
+        <v>65-71</v>
       </c>
       <c r="H190" s="1">
         <v>0.25</v>
@@ -9352,7 +9352,7 @@
         <v>64-66</v>
       </c>
       <c r="G191" t="str">
-        <v>66-73</v>
+        <v>65-71</v>
       </c>
       <c r="H191" s="1">
         <v>0.25</v>
@@ -9399,7 +9399,7 @@
         <v>66-68</v>
       </c>
       <c r="G192" t="str">
-        <v>67-74</v>
+        <v>67-73</v>
       </c>
       <c r="H192" s="1">
         <v>0.25</v>
@@ -9446,7 +9446,7 @@
         <v>66-68</v>
       </c>
       <c r="G193" t="str">
-        <v>67-74</v>
+        <v>67-73</v>
       </c>
       <c r="H193" s="1">
         <v>0.25</v>
@@ -9493,7 +9493,7 @@
         <v>66-68</v>
       </c>
       <c r="G194" t="str">
-        <v>67-74</v>
+        <v>67-73</v>
       </c>
       <c r="H194" s="1">
         <v>0.25</v>
@@ -9540,7 +9540,7 @@
         <v>66-68</v>
       </c>
       <c r="G195" t="str">
-        <v>67-74</v>
+        <v>67-73</v>
       </c>
       <c r="H195" s="1">
         <v>0.25</v>
@@ -9587,7 +9587,7 @@
         <v>67-69</v>
       </c>
       <c r="G196" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H196" s="1">
         <v>0.14</v>
@@ -9634,7 +9634,7 @@
         <v>67-69</v>
       </c>
       <c r="G197" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H197" s="1">
         <v>0.14</v>
@@ -9681,7 +9681,7 @@
         <v>67-69</v>
       </c>
       <c r="G198" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H198" s="1">
         <v>0.14</v>
@@ -9728,7 +9728,7 @@
         <v>67-69</v>
       </c>
       <c r="G199" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H199" s="1">
         <v>0.14</v>
@@ -9775,7 +9775,7 @@
         <v>67-69</v>
       </c>
       <c r="G200" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H200" s="1">
         <v>0.14</v>
@@ -9822,7 +9822,7 @@
         <v>67-69</v>
       </c>
       <c r="G201" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H201" s="1">
         <v>0.14</v>
@@ -9869,7 +9869,7 @@
         <v>67-69</v>
       </c>
       <c r="G202" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H202" s="1">
         <v>0.16</v>
@@ -9916,7 +9916,7 @@
         <v>69-71</v>
       </c>
       <c r="G203" t="str">
-        <v>71-79</v>
+        <v>71-78</v>
       </c>
       <c r="H203" s="1">
         <v>0.33</v>
@@ -9963,7 +9963,7 @@
         <v>69-71</v>
       </c>
       <c r="G204" t="str">
-        <v>71-79</v>
+        <v>71-78</v>
       </c>
       <c r="H204" s="1">
         <v>0.33</v>
@@ -10010,7 +10010,7 @@
         <v>69-71</v>
       </c>
       <c r="G205" t="str">
-        <v>71-79</v>
+        <v>71-78</v>
       </c>
       <c r="H205" s="1">
         <v>0.34</v>
@@ -10057,7 +10057,7 @@
         <v>71-73</v>
       </c>
       <c r="G206" t="str">
-        <v>73-81</v>
+        <v>72-79</v>
       </c>
       <c r="H206" s="1">
         <v>0.25</v>
@@ -10104,7 +10104,7 @@
         <v>71-73</v>
       </c>
       <c r="G207" t="str">
-        <v>73-81</v>
+        <v>72-79</v>
       </c>
       <c r="H207" s="1">
         <v>0.25</v>
@@ -10151,7 +10151,7 @@
         <v>71-73</v>
       </c>
       <c r="G208" t="str">
-        <v>73-81</v>
+        <v>72-79</v>
       </c>
       <c r="H208" s="1">
         <v>0.25</v>
@@ -10198,7 +10198,7 @@
         <v>71-73</v>
       </c>
       <c r="G209" t="str">
-        <v>73-81</v>
+        <v>72-79</v>
       </c>
       <c r="H209" s="1">
         <v>0.25</v>
@@ -10245,7 +10245,7 @@
         <v>73-75</v>
       </c>
       <c r="G210" t="str">
-        <v>74-82</v>
+        <v>74-81</v>
       </c>
       <c r="H210" s="1">
         <v>0.25</v>
@@ -10292,7 +10292,7 @@
         <v>73-75</v>
       </c>
       <c r="G211" t="str">
-        <v>74-82</v>
+        <v>74-81</v>
       </c>
       <c r="H211" s="1">
         <v>0.25</v>
@@ -10339,7 +10339,7 @@
         <v>73-75</v>
       </c>
       <c r="G212" t="str">
-        <v>74-82</v>
+        <v>74-81</v>
       </c>
       <c r="H212" s="1">
         <v>0.25</v>
@@ -10386,7 +10386,7 @@
         <v>73-75</v>
       </c>
       <c r="G213" t="str">
-        <v>74-82</v>
+        <v>74-81</v>
       </c>
       <c r="H213" s="1">
         <v>0.25</v>
@@ -10527,7 +10527,7 @@
         <v>85-87</v>
       </c>
       <c r="G216" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H216" s="1">
         <v>0.16</v>
@@ -10574,7 +10574,7 @@
         <v>85-87</v>
       </c>
       <c r="G217" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H217" s="1">
         <v>0.16</v>
@@ -10621,7 +10621,7 @@
         <v>85-87</v>
       </c>
       <c r="G218" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H218" s="1">
         <v>0.16</v>
@@ -10668,7 +10668,7 @@
         <v>85-87</v>
       </c>
       <c r="G219" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H219" s="1">
         <v>0.16</v>
@@ -10715,7 +10715,7 @@
         <v>85-87</v>
       </c>
       <c r="G220" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H220" s="1">
         <v>0.16</v>
@@ -10762,7 +10762,7 @@
         <v>85-87</v>
       </c>
       <c r="G221" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H221" s="1">
         <v>0.2</v>
@@ -10809,7 +10809,7 @@
         <v>85-87</v>
       </c>
       <c r="G222" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H222" s="1">
         <v>0.2</v>
@@ -10856,7 +10856,7 @@
         <v>85-87</v>
       </c>
       <c r="G223" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H223" s="1">
         <v>0.2</v>
@@ -10903,7 +10903,7 @@
         <v>85-87</v>
       </c>
       <c r="G224" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H224" s="1">
         <v>0.2</v>
@@ -10950,7 +10950,7 @@
         <v>85-87</v>
       </c>
       <c r="G225" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H225" s="1">
         <v>0.2</v>
@@ -10997,7 +10997,7 @@
         <v>85-87</v>
       </c>
       <c r="G226" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H226" s="1">
         <v>0.2</v>
@@ -11044,7 +11044,7 @@
         <v>85-87</v>
       </c>
       <c r="G227" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H227" s="1">
         <v>0.25</v>
@@ -11091,7 +11091,7 @@
         <v>85-87</v>
       </c>
       <c r="G228" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H228" s="1">
         <v>0.25</v>
@@ -11138,7 +11138,7 @@
         <v>85-87</v>
       </c>
       <c r="G229" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H229" s="1">
         <v>0.25</v>
@@ -11185,7 +11185,7 @@
         <v>85-87</v>
       </c>
       <c r="G230" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H230" s="1">
         <v>0.25</v>
@@ -11232,7 +11232,7 @@
         <v>85-87</v>
       </c>
       <c r="G231" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H231" s="1">
         <v>0.25</v>
@@ -11279,7 +11279,7 @@
         <v>85-87</v>
       </c>
       <c r="G232" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H232" s="1">
         <v>0.25</v>
@@ -11326,7 +11326,7 @@
         <v>85-87</v>
       </c>
       <c r="G233" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H233" s="1">
         <v>0.25</v>
@@ -11373,7 +11373,7 @@
         <v>85-87</v>
       </c>
       <c r="G234" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H234" s="1">
         <v>0.25</v>
@@ -11420,7 +11420,7 @@
         <v>85-87</v>
       </c>
       <c r="G235" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H235" s="1">
         <v>0.16</v>
@@ -11467,7 +11467,7 @@
         <v>85-87</v>
       </c>
       <c r="G236" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H236" s="1">
         <v>0.16</v>
@@ -11514,7 +11514,7 @@
         <v>85-87</v>
       </c>
       <c r="G237" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H237" s="1">
         <v>0.16</v>
@@ -11561,7 +11561,7 @@
         <v>85-87</v>
       </c>
       <c r="G238" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H238" s="1">
         <v>0.16</v>
@@ -11608,7 +11608,7 @@
         <v>85-87</v>
       </c>
       <c r="G239" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H239" s="1">
         <v>0.16</v>
@@ -11655,7 +11655,7 @@
         <v>85-87</v>
       </c>
       <c r="G240" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H240" s="1">
         <v>0.2</v>
@@ -11702,7 +11702,7 @@
         <v>90-92</v>
       </c>
       <c r="G241" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H241" s="1">
         <v>0.33</v>
@@ -11749,7 +11749,7 @@
         <v>90-92</v>
       </c>
       <c r="G242" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H242" s="1">
         <v>0.33</v>
@@ -11796,7 +11796,7 @@
         <v>90-92</v>
       </c>
       <c r="G243" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H243" s="1">
         <v>0.34</v>
@@ -11843,7 +11843,7 @@
         <v>90-92</v>
       </c>
       <c r="G244" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H244" s="1">
         <v>0.25</v>
@@ -11890,7 +11890,7 @@
         <v>90-92</v>
       </c>
       <c r="G245" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H245" s="1">
         <v>0.25</v>
@@ -11937,7 +11937,7 @@
         <v>90-92</v>
       </c>
       <c r="G246" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H246" s="1">
         <v>0.25</v>
@@ -11984,7 +11984,7 @@
         <v>90-92</v>
       </c>
       <c r="G247" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H247" s="1">
         <v>0.25</v>
@@ -12031,7 +12031,7 @@
         <v>90-92</v>
       </c>
       <c r="G248" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H248" s="1">
         <v>0.25</v>
@@ -12078,7 +12078,7 @@
         <v>90-92</v>
       </c>
       <c r="G249" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H249" s="1">
         <v>0.25</v>
@@ -12125,7 +12125,7 @@
         <v>90-92</v>
       </c>
       <c r="G250" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H250" s="1">
         <v>0.25</v>
@@ -12172,7 +12172,7 @@
         <v>90-92</v>
       </c>
       <c r="G251" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H251" s="1">
         <v>0.25</v>
@@ -12219,7 +12219,7 @@
         <v>85-87</v>
       </c>
       <c r="G252" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H252" s="1">
         <v>0.14</v>
@@ -12266,7 +12266,7 @@
         <v>85-87</v>
       </c>
       <c r="G253" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H253" s="1">
         <v>0.14</v>
@@ -12313,7 +12313,7 @@
         <v>85-87</v>
       </c>
       <c r="G254" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H254" s="1">
         <v>0.14</v>
@@ -12360,7 +12360,7 @@
         <v>85-87</v>
       </c>
       <c r="G255" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H255" s="1">
         <v>0.14</v>
@@ -12407,7 +12407,7 @@
         <v>85-87</v>
       </c>
       <c r="G256" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H256" s="1">
         <v>0.14</v>
@@ -12454,7 +12454,7 @@
         <v>85-87</v>
       </c>
       <c r="G257" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H257" s="1">
         <v>0.14</v>
@@ -12501,7 +12501,7 @@
         <v>85-87</v>
       </c>
       <c r="G258" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H258" s="1">
         <v>0.16</v>
@@ -12548,7 +12548,7 @@
         <v>90-92</v>
       </c>
       <c r="G259" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H259" s="1">
         <v>0.25</v>
@@ -12595,7 +12595,7 @@
         <v>90-92</v>
       </c>
       <c r="G260" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H260" s="1">
         <v>0.25</v>
@@ -12642,7 +12642,7 @@
         <v>90-92</v>
       </c>
       <c r="G261" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H261" s="1">
         <v>0.25</v>
@@ -12689,7 +12689,7 @@
         <v>90-92</v>
       </c>
       <c r="G262" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H262" s="1">
         <v>0.25</v>
@@ -12736,7 +12736,7 @@
         <v>90-92</v>
       </c>
       <c r="G263" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H263" s="1">
         <v>0.33</v>
@@ -12783,7 +12783,7 @@
         <v>90-92</v>
       </c>
       <c r="G264" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H264" s="1">
         <v>0.33</v>
@@ -12830,7 +12830,7 @@
         <v>90-92</v>
       </c>
       <c r="G265" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H265" s="1">
         <v>0.34</v>
@@ -12877,7 +12877,7 @@
         <v>100-100</v>
       </c>
       <c r="G266" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H266" s="1">
         <v>0.02</v>
@@ -12924,7 +12924,7 @@
         <v>100-100</v>
       </c>
       <c r="G267" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H267" s="1">
         <v>0.02</v>
@@ -12971,7 +12971,7 @@
         <v>100-100</v>
       </c>
       <c r="G268" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H268" s="1">
         <v>0.02</v>
@@ -13018,7 +13018,7 @@
         <v>100-100</v>
       </c>
       <c r="G269" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H269" s="1">
         <v>0.02</v>
@@ -13065,7 +13065,7 @@
         <v>100-100</v>
       </c>
       <c r="G270" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H270" s="1">
         <v>0.02</v>
@@ -13112,7 +13112,7 @@
         <v>100-100</v>
       </c>
       <c r="G271" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H271" s="1">
         <v>0.02</v>
@@ -13159,7 +13159,7 @@
         <v>100-100</v>
       </c>
       <c r="G272" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H272" s="1">
         <v>0.02</v>
@@ -13206,7 +13206,7 @@
         <v>100-100</v>
       </c>
       <c r="G273" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H273" s="1">
         <v>0.02</v>
@@ -13253,7 +13253,7 @@
         <v>100-100</v>
       </c>
       <c r="G274" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H274" s="1">
         <v>0.02</v>
@@ -13300,7 +13300,7 @@
         <v>100-100</v>
       </c>
       <c r="G275" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H275" s="1">
         <v>0.02</v>
@@ -13347,7 +13347,7 @@
         <v>100-100</v>
       </c>
       <c r="G276" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H276" s="1">
         <v>0.02</v>
@@ -13394,7 +13394,7 @@
         <v>100-100</v>
       </c>
       <c r="G277" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H277" s="1">
         <v>0.02</v>
@@ -13441,7 +13441,7 @@
         <v>100-100</v>
       </c>
       <c r="G278" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H278" s="1">
         <v>0.02</v>
@@ -13488,7 +13488,7 @@
         <v>100-100</v>
       </c>
       <c r="G279" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H279" s="1">
         <v>0.02</v>
@@ -13535,7 +13535,7 @@
         <v>100-100</v>
       </c>
       <c r="G280" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H280" s="1">
         <v>0.02</v>
@@ -13582,7 +13582,7 @@
         <v>100-100</v>
       </c>
       <c r="G281" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H281" s="1">
         <v>0.02</v>
@@ -13629,7 +13629,7 @@
         <v>100-100</v>
       </c>
       <c r="G282" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H282" s="1">
         <v>0.02</v>
@@ -13676,7 +13676,7 @@
         <v>100-100</v>
       </c>
       <c r="G283" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H283" s="1">
         <v>0.02</v>
@@ -13723,7 +13723,7 @@
         <v>100-100</v>
       </c>
       <c r="G284" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H284" s="1">
         <v>0.02</v>
@@ -13770,7 +13770,7 @@
         <v>100-100</v>
       </c>
       <c r="G285" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H285" s="1">
         <v>0.02</v>
@@ -13817,7 +13817,7 @@
         <v>100-100</v>
       </c>
       <c r="G286" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H286" s="1">
         <v>0.02</v>
@@ -13864,7 +13864,7 @@
         <v>100-100</v>
       </c>
       <c r="G287" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H287" s="1">
         <v>0.02</v>
@@ -13911,7 +13911,7 @@
         <v>100-100</v>
       </c>
       <c r="G288" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H288" s="1">
         <v>0.02</v>
@@ -13958,7 +13958,7 @@
         <v>100-100</v>
       </c>
       <c r="G289" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H289" s="1">
         <v>0.02</v>
@@ -14005,7 +14005,7 @@
         <v>100-100</v>
       </c>
       <c r="G290" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H290" s="1">
         <v>0.02</v>
@@ -14052,7 +14052,7 @@
         <v>100-100</v>
       </c>
       <c r="G291" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H291" s="1">
         <v>0.02</v>
@@ -14099,7 +14099,7 @@
         <v>100-100</v>
       </c>
       <c r="G292" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H292" s="1">
         <v>0.02</v>
@@ -14146,7 +14146,7 @@
         <v>100-100</v>
       </c>
       <c r="G293" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H293" s="1">
         <v>0.02</v>
@@ -14193,7 +14193,7 @@
         <v>100-100</v>
       </c>
       <c r="G294" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H294" s="1">
         <v>0.02</v>
@@ -14240,7 +14240,7 @@
         <v>100-100</v>
       </c>
       <c r="G295" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H295" s="1">
         <v>0.02</v>
@@ -14287,7 +14287,7 @@
         <v>100-100</v>
       </c>
       <c r="G296" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H296" s="1">
         <v>0.02</v>
@@ -14334,7 +14334,7 @@
         <v>100-100</v>
       </c>
       <c r="G297" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H297" s="1">
         <v>0.02</v>
@@ -14381,7 +14381,7 @@
         <v>100-100</v>
       </c>
       <c r="G298" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H298" s="1">
         <v>0.02</v>
@@ -14428,7 +14428,7 @@
         <v>100-100</v>
       </c>
       <c r="G299" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H299" s="1">
         <v>0.02</v>
@@ -14475,7 +14475,7 @@
         <v>100-100</v>
       </c>
       <c r="G300" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H300" s="1">
         <v>0.02</v>
@@ -14522,7 +14522,7 @@
         <v>100-100</v>
       </c>
       <c r="G301" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H301" s="1">
         <v>0.02</v>
@@ -14569,7 +14569,7 @@
         <v>100-100</v>
       </c>
       <c r="G302" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H302" s="1">
         <v>0.02</v>
@@ -14616,7 +14616,7 @@
         <v>100-100</v>
       </c>
       <c r="G303" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H303" s="1">
         <v>0.02</v>
@@ -14663,7 +14663,7 @@
         <v>100-100</v>
       </c>
       <c r="G304" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H304" s="1">
         <v>0.02</v>
@@ -14710,7 +14710,7 @@
         <v>100-100</v>
       </c>
       <c r="G305" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H305" s="1">
         <v>0.02</v>
@@ -14757,7 +14757,7 @@
         <v>100-100</v>
       </c>
       <c r="G306" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H306" s="1">
         <v>0.02</v>
@@ -14804,13 +14804,13 @@
         <v>100-100</v>
       </c>
       <c r="G307" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H307" s="1">
         <v>0.18</v>
       </c>
-      <c r="I307" t="str">
-        <v/>
+      <c r="I307" s="1">
+        <v>0.023809523809523808</v>
       </c>
       <c r="J307" t="str">
         <v>Yes</v>
@@ -14851,7 +14851,7 @@
         <v>85-87</v>
       </c>
       <c r="G308" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H308" s="1">
         <v>0.16</v>
@@ -14898,7 +14898,7 @@
         <v>85-87</v>
       </c>
       <c r="G309" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H309" s="1">
         <v>0.16</v>
@@ -14945,7 +14945,7 @@
         <v>85-87</v>
       </c>
       <c r="G310" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H310" s="1">
         <v>0.16</v>
@@ -14992,7 +14992,7 @@
         <v>85-87</v>
       </c>
       <c r="G311" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H311" s="1">
         <v>0.16</v>
@@ -15039,7 +15039,7 @@
         <v>85-87</v>
       </c>
       <c r="G312" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H312" s="1">
         <v>0.16</v>
@@ -15086,7 +15086,7 @@
         <v>85-87</v>
       </c>
       <c r="G313" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H313" s="1">
         <v>0.2</v>
@@ -15133,7 +15133,7 @@
         <v>95-97</v>
       </c>
       <c r="G314" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H314" s="1">
         <v>0.2</v>
@@ -15180,7 +15180,7 @@
         <v>95-97</v>
       </c>
       <c r="G315" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H315" s="1">
         <v>0.2</v>
@@ -15227,7 +15227,7 @@
         <v>95-97</v>
       </c>
       <c r="G316" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H316" s="1">
         <v>0.2</v>
@@ -15274,7 +15274,7 @@
         <v>95-97</v>
       </c>
       <c r="G317" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H317" s="1">
         <v>0.2</v>
@@ -15321,7 +15321,7 @@
         <v>95-97</v>
       </c>
       <c r="G318" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H318" s="1">
         <v>0.2</v>
@@ -15368,7 +15368,7 @@
         <v>100-100</v>
       </c>
       <c r="G319" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H319" s="1">
         <v>0.33</v>
@@ -15415,7 +15415,7 @@
         <v>100-100</v>
       </c>
       <c r="G320" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H320" s="1">
         <v>0.33</v>
@@ -15462,7 +15462,7 @@
         <v>100-100</v>
       </c>
       <c r="G321" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H321" s="1">
         <v>0.34</v>
@@ -15509,7 +15509,7 @@
         <v>85-87</v>
       </c>
       <c r="G322" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H322" s="1">
         <v>0.33</v>
@@ -15556,7 +15556,7 @@
         <v>85-87</v>
       </c>
       <c r="G323" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H323" s="1">
         <v>0.33</v>
@@ -15603,7 +15603,7 @@
         <v>85-87</v>
       </c>
       <c r="G324" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H324" s="1">
         <v>0.34</v>
@@ -15650,7 +15650,7 @@
         <v>95-97</v>
       </c>
       <c r="G325" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H325" s="1">
         <v>0.5</v>
@@ -15697,7 +15697,7 @@
         <v>95-97</v>
       </c>
       <c r="G326" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H326" s="1">
         <v>0.5</v>
@@ -15744,7 +15744,7 @@
         <v>110-110</v>
       </c>
       <c r="G327" t="str">
-        <v>76-84</v>
+        <v>110-110</v>
       </c>
       <c r="H327" s="1">
         <v>0.25</v>
@@ -15791,7 +15791,7 @@
         <v>110-110</v>
       </c>
       <c r="G328" t="str">
-        <v>76-84</v>
+        <v>110-110</v>
       </c>
       <c r="H328" s="1">
         <v>0.25</v>
@@ -15838,7 +15838,7 @@
         <v>110-110</v>
       </c>
       <c r="G329" t="str">
-        <v>76-84</v>
+        <v>110-110</v>
       </c>
       <c r="H329" s="1">
         <v>0.25</v>
@@ -15885,7 +15885,7 @@
         <v>110-110</v>
       </c>
       <c r="G330" t="str">
-        <v>76-84</v>
+        <v>110-110</v>
       </c>
       <c r="H330" s="1">
         <v>0.25</v>
@@ -15932,7 +15932,7 @@
         <v>82-84</v>
       </c>
       <c r="G331" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H331" s="1">
         <v>0.25</v>
@@ -15979,7 +15979,7 @@
         <v>82-84</v>
       </c>
       <c r="G332" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H332" s="1">
         <v>0.25</v>
@@ -16026,7 +16026,7 @@
         <v>82-84</v>
       </c>
       <c r="G333" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H333" s="1">
         <v>0.25</v>
@@ -16073,7 +16073,7 @@
         <v>82-84</v>
       </c>
       <c r="G334" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H334" s="1">
         <v>0.25</v>
@@ -16120,7 +16120,7 @@
         <v>82-84</v>
       </c>
       <c r="G335" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H335" s="1">
         <v>0.25</v>
@@ -16167,7 +16167,7 @@
         <v>82-84</v>
       </c>
       <c r="G336" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H336" s="1">
         <v>0.25</v>
@@ -16214,7 +16214,7 @@
         <v>82-84</v>
       </c>
       <c r="G337" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H337" s="1">
         <v>0.25</v>
@@ -16261,7 +16261,7 @@
         <v>82-84</v>
       </c>
       <c r="G338" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H338" s="1">
         <v>0.25</v>
@@ -16308,7 +16308,7 @@
         <v>100-100</v>
       </c>
       <c r="G339" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H339" s="1">
         <v>0.33</v>
@@ -16355,7 +16355,7 @@
         <v>100-100</v>
       </c>
       <c r="G340" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H340" s="1">
         <v>0.33</v>
@@ -16402,7 +16402,7 @@
         <v>100-100</v>
       </c>
       <c r="G341" t="str">
-        <v>76-84</v>
+        <v>76-83</v>
       </c>
       <c r="H341" s="1">
         <v>0.34</v>
@@ -16449,7 +16449,7 @@
         <v>82-84</v>
       </c>
       <c r="G342" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H342" s="1">
         <v>0.2</v>
@@ -16496,7 +16496,7 @@
         <v>82-84</v>
       </c>
       <c r="G343" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H343" s="1">
         <v>0.2</v>
@@ -16543,7 +16543,7 @@
         <v>82-84</v>
       </c>
       <c r="G344" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H344" s="1">
         <v>0.2</v>
@@ -16590,7 +16590,7 @@
         <v>82-84</v>
       </c>
       <c r="G345" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H345" s="1">
         <v>0.2</v>
@@ -16637,7 +16637,7 @@
         <v>82-84</v>
       </c>
       <c r="G346" t="str">
-        <v>76-84</v>
+        <v>96-104</v>
       </c>
       <c r="H346" s="1">
         <v>0.2</v>
@@ -16731,7 +16731,7 @@
         <v>120-120</v>
       </c>
       <c r="G348" t="str">
-        <v>76-84</v>
+        <v>120-120</v>
       </c>
       <c r="H348" s="1">
         <v>0.25</v>
@@ -16778,7 +16778,7 @@
         <v>120-120</v>
       </c>
       <c r="G349" t="str">
-        <v>76-84</v>
+        <v>120-120</v>
       </c>
       <c r="H349" s="1">
         <v>0.25</v>
@@ -16825,7 +16825,7 @@
         <v>120-120</v>
       </c>
       <c r="G350" t="str">
-        <v>76-84</v>
+        <v>120-120</v>
       </c>
       <c r="H350" s="1">
         <v>0.25</v>
@@ -16872,7 +16872,7 @@
         <v>120-120</v>
       </c>
       <c r="G351" t="str">
-        <v>76-84</v>
+        <v>120-120</v>
       </c>
       <c r="H351" s="1">
         <v>0.25</v>

--- a/9_Hisui_Data.xlsx
+++ b/9_Hisui_Data.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O351"/>
+  <dimension ref="A1:O357"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -501,7 +501,7 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C3" t="str">
         <v>Aspiration Hill</v>
@@ -534,10 +534,10 @@
         <v>No</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>Horseshoe Plains</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Aspiration Hill","count":10}}</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -548,7 +548,7 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C4" t="str">
         <v>Aspiration Hill</v>
@@ -581,10 +581,10 @@
         <v>No</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>Horseshoe Plains</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Aspiration Hill","count":10}}</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -595,7 +595,7 @@
         <v/>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C5" t="str">
         <v>Aspiration Hill</v>
@@ -628,10 +628,10 @@
         <v>No</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>Horseshoe Plains</v>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Aspiration Hill","count":10}}</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -686,10 +686,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C7" t="str">
         <v>Horseshoe Plains</v>
@@ -722,10 +722,10 @@
         <v>No</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>Deertrack Path</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Horseshoe Plains","count":10}}</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -733,10 +733,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C8" t="str">
         <v>Horseshoe Plains</v>
@@ -769,10 +769,10 @@
         <v>No</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>Deertrack Path</v>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Horseshoe Plains","count":10}}</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -827,10 +827,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C10" t="str">
         <v>Deertrack Path</v>
@@ -863,10 +863,10 @@
         <v>No</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>Deertrack Heights</v>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deertrack Path","count":10}}</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -874,10 +874,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C11" t="str">
         <v>Deertrack Path</v>
@@ -910,10 +910,10 @@
         <v>No</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>Deertrack Heights</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deertrack Path","count":10}}</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -921,10 +921,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C12" t="str">
         <v>Deertrack Path</v>
@@ -957,10 +957,10 @@
         <v>No</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>Deertrack Heights</v>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deertrack Path","count":10}}</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -968,10 +968,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C13" t="str">
         <v>Deertrack Path</v>
@@ -1004,10 +1004,10 @@
         <v>No</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>Deertrack Heights</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deertrack Path","count":10}}</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B14" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C14" t="str">
         <v>Deertrack Path</v>
@@ -1038,8 +1038,8 @@
       <c r="H14" s="1">
         <v>0.2</v>
       </c>
-      <c r="I14" t="str">
-        <v/>
+      <c r="I14" s="1">
+        <v>0.15</v>
       </c>
       <c r="J14" t="str">
         <v>Yes</v>
@@ -1051,10 +1051,10 @@
         <v>No</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>Deertrack Heights</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deertrack Path","count":10}}</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B16" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C16" t="str">
         <v>Deertrack Heights</v>
@@ -1145,10 +1145,10 @@
         <v>No</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>Gym - Kleavor, Droning Meadow, Grueling Grove</v>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deertrack Heights","count":10}}</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C17" t="str">
         <v>Deertrack Heights</v>
@@ -1192,10 +1192,10 @@
         <v>No</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>Gym - Kleavor, Droning Meadow, Grueling Grove</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deertrack Heights","count":10}}</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C18" t="str">
         <v>Deertrack Heights</v>
@@ -1239,10 +1239,10 @@
         <v>No</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>Gym - Kleavor, Droning Meadow, Grueling Grove</v>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deertrack Heights","count":10}}</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C19" t="str">
         <v>Deertrack Heights</v>
@@ -1286,10 +1286,10 @@
         <v>No</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>Gym - Kleavor, Droning Meadow, Grueling Grove</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deertrack Heights","count":10}}</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C20" t="str">
         <v>Deertrack Heights</v>
@@ -1333,10 +1333,10 @@
         <v>No</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>Gym - Kleavor, Droning Meadow, Grueling Grove</v>
       </c>
       <c r="N20" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deertrack Heights","count":10}}</v>
       </c>
       <c r="O20" t="str">
         <v/>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C21" t="str">
         <v>Deertrack Heights</v>
@@ -1380,10 +1380,10 @@
         <v>No</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>Gym - Kleavor, Droning Meadow, Grueling Grove</v>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deertrack Heights","count":10}}</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B24" t="str">
         <v/>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B25" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B26" t="str">
         <v/>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B27" t="str">
         <v/>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B28" t="str">
         <v/>
@@ -1696,8 +1696,8 @@
       <c r="H28" s="1">
         <v>0.2</v>
       </c>
-      <c r="I28" t="str">
-        <v/>
+      <c r="I28" s="1">
+        <v>0.15</v>
       </c>
       <c r="J28" t="str">
         <v>Yes</v>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B30" t="str">
         <v/>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B31" t="str">
         <v/>
@@ -1861,7 +1861,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C35" t="str">
         <v>Oreburrow Tunnel</v>
@@ -2038,10 +2038,10 @@
         <v>No</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>Nature’s Pantry</v>
       </c>
       <c r="N35" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Oreburrow Tunnel","count":10}}</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C36" t="str">
         <v>Oreburrow Tunnel</v>
@@ -2085,10 +2085,10 @@
         <v>No</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>Nature’s Pantry</v>
       </c>
       <c r="N36" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Oreburrow Tunnel","count":10}}</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C37" t="str">
         <v>Oreburrow Tunnel</v>
@@ -2132,10 +2132,10 @@
         <v>No</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>Nature’s Pantry</v>
       </c>
       <c r="N37" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Oreburrow Tunnel","count":10}}</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C38" t="str">
         <v>Oreburrow Tunnel</v>
@@ -2179,10 +2179,10 @@
         <v>No</v>
       </c>
       <c r="M38" t="str">
-        <v/>
+        <v>Nature’s Pantry</v>
       </c>
       <c r="N38" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Oreburrow Tunnel","count":10}}</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C39" t="str">
         <v>Oreburrow Tunnel</v>
@@ -2213,8 +2213,8 @@
       <c r="H39" s="1">
         <v>0.2</v>
       </c>
-      <c r="I39" t="str">
-        <v/>
+      <c r="I39" s="1">
+        <v>0.15</v>
       </c>
       <c r="J39" t="str">
         <v>Legacy</v>
@@ -2226,10 +2226,10 @@
         <v>No</v>
       </c>
       <c r="M39" t="str">
-        <v/>
+        <v>Nature’s Pantry</v>
       </c>
       <c r="N39" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Oreburrow Tunnel","count":10}}</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C41" t="str">
         <v>Nature’s Pantry</v>
@@ -2320,10 +2320,10 @@
         <v>No</v>
       </c>
       <c r="M41" t="str">
-        <v/>
+        <v>The Heartwood North</v>
       </c>
       <c r="N41" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Nature’s Pantry","count":10}}</v>
       </c>
       <c r="O41" t="str">
         <v/>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B42" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C42" t="str">
         <v>Nature’s Pantry</v>
@@ -2367,10 +2367,10 @@
         <v>No</v>
       </c>
       <c r="M42" t="str">
-        <v/>
+        <v>The Heartwood North</v>
       </c>
       <c r="N42" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Nature’s Pantry","count":10}}</v>
       </c>
       <c r="O42" t="str">
         <v/>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B43" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C43" t="str">
         <v>Nature’s Pantry</v>
@@ -2414,10 +2414,10 @@
         <v>No</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>The Heartwood North</v>
       </c>
       <c r="N43" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Nature’s Pantry","count":10}}</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B44" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C44" t="str">
         <v>Nature’s Pantry</v>
@@ -2461,10 +2461,10 @@
         <v>No</v>
       </c>
       <c r="M44" t="str">
-        <v/>
+        <v>The Heartwood North</v>
       </c>
       <c r="N44" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Nature’s Pantry","count":10}}</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B45" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C45" t="str">
         <v>Nature’s Pantry</v>
@@ -2508,10 +2508,10 @@
         <v>No</v>
       </c>
       <c r="M45" t="str">
-        <v/>
+        <v>The Heartwood North</v>
       </c>
       <c r="N45" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Nature’s Pantry","count":10}}</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B46" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C46" t="str">
         <v>Nature’s Pantry</v>
@@ -2555,10 +2555,10 @@
         <v>No</v>
       </c>
       <c r="M46" t="str">
-        <v/>
+        <v>The Heartwood North</v>
       </c>
       <c r="N46" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Nature’s Pantry","count":10}}</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B48" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C48" t="str">
         <v>The Heartwood North</v>
@@ -2649,10 +2649,10 @@
         <v>No</v>
       </c>
       <c r="M48" t="str">
-        <v/>
+        <v>The Heartwood South</v>
       </c>
       <c r="N48" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"The Heartwood North","count":10}}</v>
       </c>
       <c r="O48" t="str">
         <v/>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B49" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C49" t="str">
         <v>The Heartwood North</v>
@@ -2696,10 +2696,10 @@
         <v>No</v>
       </c>
       <c r="M49" t="str">
-        <v/>
+        <v>The Heartwood South</v>
       </c>
       <c r="N49" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"The Heartwood North","count":10}}</v>
       </c>
       <c r="O49" t="str">
         <v/>
@@ -2707,10 +2707,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B50" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C50" t="str">
         <v>The Heartwood North</v>
@@ -2743,10 +2743,10 @@
         <v>No</v>
       </c>
       <c r="M50" t="str">
-        <v/>
+        <v>The Heartwood South</v>
       </c>
       <c r="N50" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"The Heartwood North","count":10}}</v>
       </c>
       <c r="O50" t="str">
         <v/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B51" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C51" t="str">
         <v>The Heartwood North</v>
@@ -2790,10 +2790,10 @@
         <v>No</v>
       </c>
       <c r="M51" t="str">
-        <v/>
+        <v>The Heartwood South</v>
       </c>
       <c r="N51" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"The Heartwood North","count":10}}</v>
       </c>
       <c r="O51" t="str">
         <v/>
@@ -2801,10 +2801,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C52" t="str">
         <v>The Heartwood North</v>
@@ -2837,10 +2837,10 @@
         <v>No</v>
       </c>
       <c r="M52" t="str">
-        <v/>
+        <v>The Heartwood South</v>
       </c>
       <c r="N52" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"The Heartwood North","count":10}}</v>
       </c>
       <c r="O52" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C53" t="str">
         <v>The Heartwood North</v>
@@ -2884,10 +2884,10 @@
         <v>No</v>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>The Heartwood South</v>
       </c>
       <c r="N53" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"The Heartwood North","count":10}}</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B55" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C55" t="str">
         <v>The Heartwood South</v>
@@ -2978,10 +2978,10 @@
         <v>No</v>
       </c>
       <c r="M55" t="str">
-        <v/>
+        <v>Golden Lowlands North</v>
       </c>
       <c r="N55" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"The Heartwood South","count":10}}</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -2989,10 +2989,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B56" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C56" t="str">
         <v>The Heartwood South</v>
@@ -3025,10 +3025,10 @@
         <v>No</v>
       </c>
       <c r="M56" t="str">
-        <v/>
+        <v>Golden Lowlands North</v>
       </c>
       <c r="N56" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"The Heartwood South","count":10}}</v>
       </c>
       <c r="O56" t="str">
         <v/>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C57" t="str">
         <v>The Heartwood South</v>
@@ -3072,10 +3072,10 @@
         <v>No</v>
       </c>
       <c r="M57" t="str">
-        <v/>
+        <v>Golden Lowlands North</v>
       </c>
       <c r="N57" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"The Heartwood South","count":10}}</v>
       </c>
       <c r="O57" t="str">
         <v/>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C58" t="str">
         <v>The Heartwood South</v>
@@ -3119,10 +3119,10 @@
         <v>No</v>
       </c>
       <c r="M58" t="str">
-        <v/>
+        <v>Golden Lowlands North</v>
       </c>
       <c r="N58" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"The Heartwood South","count":10}}</v>
       </c>
       <c r="O58" t="str">
         <v/>
@@ -3177,10 +3177,10 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="C60" t="str">
         <v>Golden Lowlands North</v>
@@ -3213,10 +3213,10 @@
         <v>No</v>
       </c>
       <c r="M60" t="str">
-        <v/>
+        <v>Golden Lowlands South</v>
       </c>
       <c r="N60" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Golden Lowlands North","count":10}}</v>
       </c>
       <c r="O60" t="str">
         <v/>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="C61" t="str">
         <v>Golden Lowlands North</v>
@@ -3260,10 +3260,10 @@
         <v>No</v>
       </c>
       <c r="M61" t="str">
-        <v/>
+        <v>Golden Lowlands South</v>
       </c>
       <c r="N61" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Golden Lowlands North","count":10}}</v>
       </c>
       <c r="O61" t="str">
         <v/>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C63" t="str">
         <v>Golden Lowlands South</v>
@@ -3354,10 +3354,10 @@
         <v>No</v>
       </c>
       <c r="M63" t="str">
-        <v/>
+        <v>Gapejaw Bog North</v>
       </c>
       <c r="N63" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Golden Lowlands South","count":10}}</v>
       </c>
       <c r="O63" t="str">
         <v/>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C64" t="str">
         <v>Golden Lowlands South</v>
@@ -3401,10 +3401,10 @@
         <v>No</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>Gapejaw Bog North</v>
       </c>
       <c r="N64" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Golden Lowlands South","count":10}}</v>
       </c>
       <c r="O64" t="str">
         <v/>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C66" t="str">
         <v>Gapejaw Bog North</v>
@@ -3495,10 +3495,10 @@
         <v>No</v>
       </c>
       <c r="M66" t="str">
-        <v/>
+        <v>Gapejaw Bog South</v>
       </c>
       <c r="N66" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Gapejaw Bog North","count":10}}</v>
       </c>
       <c r="O66" t="str">
         <v/>
@@ -3506,10 +3506,10 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C67" t="str">
         <v>Gapejaw Bog North</v>
@@ -3542,10 +3542,10 @@
         <v>No</v>
       </c>
       <c r="M67" t="str">
-        <v/>
+        <v>Gapejaw Bog South</v>
       </c>
       <c r="N67" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Gapejaw Bog North","count":10}}</v>
       </c>
       <c r="O67" t="str">
         <v/>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C68" t="str">
         <v>Gapejaw Bog North</v>
@@ -3589,10 +3589,10 @@
         <v>No</v>
       </c>
       <c r="M68" t="str">
-        <v/>
+        <v>Gapejaw Bog South</v>
       </c>
       <c r="N68" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Gapejaw Bog North","count":10}}</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C69" t="str">
         <v>Gapejaw Bog North</v>
@@ -3636,10 +3636,10 @@
         <v>No</v>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>Gapejaw Bog South</v>
       </c>
       <c r="N69" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Gapejaw Bog North","count":10}}</v>
       </c>
       <c r="O69" t="str">
         <v/>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C70" t="str">
         <v>Gapejaw Bog North</v>
@@ -3670,8 +3670,8 @@
       <c r="H70" s="1">
         <v>0.2</v>
       </c>
-      <c r="I70" t="str">
-        <v/>
+      <c r="I70" s="1">
+        <v>0.15</v>
       </c>
       <c r="J70" t="str">
         <v>Yes</v>
@@ -3683,10 +3683,10 @@
         <v>No</v>
       </c>
       <c r="M70" t="str">
-        <v/>
+        <v>Gapejaw Bog South</v>
       </c>
       <c r="N70" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Gapejaw Bog North","count":10}}</v>
       </c>
       <c r="O70" t="str">
         <v/>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C72" t="str">
         <v>Gapejaw Bog South</v>
@@ -3777,10 +3777,10 @@
         <v>No</v>
       </c>
       <c r="M72" t="str">
-        <v/>
+        <v>Gym - Lilligant, Obsidian Falls</v>
       </c>
       <c r="N72" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Gapejaw Bog South","count":10}}</v>
       </c>
       <c r="O72" t="str">
         <v/>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C73" t="str">
         <v>Gapejaw Bog South</v>
@@ -3824,10 +3824,10 @@
         <v>No</v>
       </c>
       <c r="M73" t="str">
-        <v/>
+        <v>Gym - Lilligant, Obsidian Falls</v>
       </c>
       <c r="N73" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Gapejaw Bog South","count":10}}</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -3929,7 +3929,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B76" t="str">
         <v/>
@@ -3976,7 +3976,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B77" t="str">
         <v/>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B78" t="str">
         <v/>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B79" t="str">
         <v/>
@@ -4117,7 +4117,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B80" t="str">
         <v/>
@@ -4140,8 +4140,8 @@
       <c r="H80" s="1">
         <v>0.2</v>
       </c>
-      <c r="I80" t="str">
-        <v/>
+      <c r="I80" s="1">
+        <v>0.15</v>
       </c>
       <c r="J80" t="str">
         <v>Yes</v>
@@ -4211,10 +4211,10 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B82" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C82" t="str">
         <v>Ursa's Ring</v>
@@ -4247,10 +4247,10 @@
         <v>No</v>
       </c>
       <c r="M82" t="str">
-        <v/>
+        <v>Sludge Mound</v>
       </c>
       <c r="N82" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Ursa's Ring","count":10}}</v>
       </c>
       <c r="O82" t="str">
         <v/>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C83" t="str">
         <v>Ursa's Ring</v>
@@ -4294,10 +4294,10 @@
         <v>No</v>
       </c>
       <c r="M83" t="str">
-        <v/>
+        <v>Sludge Mound</v>
       </c>
       <c r="N83" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Ursa's Ring","count":10}}</v>
       </c>
       <c r="O83" t="str">
         <v/>
@@ -4305,10 +4305,10 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B84" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C84" t="str">
         <v>Ursa's Ring</v>
@@ -4341,10 +4341,10 @@
         <v>No</v>
       </c>
       <c r="M84" t="str">
-        <v/>
+        <v>Sludge Mound</v>
       </c>
       <c r="N84" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Ursa's Ring","count":10}}</v>
       </c>
       <c r="O84" t="str">
         <v/>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B85" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C85" t="str">
         <v>Ursa's Ring</v>
@@ -4388,10 +4388,10 @@
         <v>No</v>
       </c>
       <c r="M85" t="str">
-        <v/>
+        <v>Sludge Mound</v>
       </c>
       <c r="N85" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Ursa's Ring","count":10}}</v>
       </c>
       <c r="O85" t="str">
         <v/>
@@ -4399,10 +4399,10 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B86" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C86" t="str">
         <v>Ursa's Ring</v>
@@ -4435,10 +4435,10 @@
         <v>No</v>
       </c>
       <c r="M86" t="str">
-        <v/>
+        <v>Sludge Mound</v>
       </c>
       <c r="N86" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Ursa's Ring","count":10}}</v>
       </c>
       <c r="O86" t="str">
         <v/>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B87" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C87" t="str">
         <v>Ursa's Ring</v>
@@ -4482,10 +4482,10 @@
         <v>No</v>
       </c>
       <c r="M87" t="str">
-        <v/>
+        <v>Sludge Mound</v>
       </c>
       <c r="N87" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Ursa's Ring","count":10}}</v>
       </c>
       <c r="O87" t="str">
         <v/>
@@ -4540,10 +4540,10 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B89" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C89" t="str">
         <v>Sludge Mound</v>
@@ -4576,10 +4576,10 @@
         <v>No</v>
       </c>
       <c r="M89" t="str">
-        <v/>
+        <v>Scarlet Bog</v>
       </c>
       <c r="N89" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Sludge Mound","count":10}}</v>
       </c>
       <c r="O89" t="str">
         <v/>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B90" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C90" t="str">
         <v>Sludge Mound</v>
@@ -4623,10 +4623,10 @@
         <v>No</v>
       </c>
       <c r="M90" t="str">
-        <v/>
+        <v>Scarlet Bog</v>
       </c>
       <c r="N90" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Sludge Mound","count":10}}</v>
       </c>
       <c r="O90" t="str">
         <v/>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B91" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C91" t="str">
         <v>Sludge Mound</v>
@@ -4670,10 +4670,10 @@
         <v>No</v>
       </c>
       <c r="M91" t="str">
-        <v/>
+        <v>Scarlet Bog</v>
       </c>
       <c r="N91" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Sludge Mound","count":10}}</v>
       </c>
       <c r="O91" t="str">
         <v/>
@@ -4681,10 +4681,10 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B92" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C92" t="str">
         <v>Sludge Mound</v>
@@ -4717,10 +4717,10 @@
         <v>No</v>
       </c>
       <c r="M92" t="str">
-        <v/>
+        <v>Scarlet Bog</v>
       </c>
       <c r="N92" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Sludge Mound","count":10}}</v>
       </c>
       <c r="O92" t="str">
         <v/>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B93" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C93" t="str">
         <v>Sludge Mound</v>
@@ -4751,8 +4751,8 @@
       <c r="H93" s="1">
         <v>0.2</v>
       </c>
-      <c r="I93" t="str">
-        <v/>
+      <c r="I93" s="1">
+        <v>0.15</v>
       </c>
       <c r="J93" t="str">
         <v>Yes</v>
@@ -4764,10 +4764,10 @@
         <v>No</v>
       </c>
       <c r="M93" t="str">
-        <v/>
+        <v>Scarlet Bog</v>
       </c>
       <c r="N93" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Sludge Mound","count":10}}</v>
       </c>
       <c r="O93" t="str">
         <v/>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B95" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C95" t="str">
         <v>Scarlet Bog</v>
@@ -4858,10 +4858,10 @@
         <v>No</v>
       </c>
       <c r="M95" t="str">
-        <v/>
+        <v>Bolderoll Slope</v>
       </c>
       <c r="N95" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Scarlet Bog","count":10}}</v>
       </c>
       <c r="O95" t="str">
         <v/>
@@ -4869,10 +4869,10 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B96" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C96" t="str">
         <v>Scarlet Bog</v>
@@ -4905,10 +4905,10 @@
         <v>No</v>
       </c>
       <c r="M96" t="str">
-        <v/>
+        <v>Bolderoll Slope</v>
       </c>
       <c r="N96" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Scarlet Bog","count":10}}</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B98" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C98" t="str">
         <v>Bolderoll Slope</v>
@@ -4999,10 +4999,10 @@
         <v>No</v>
       </c>
       <c r="M98" t="str">
-        <v/>
+        <v>Holm of Trials</v>
       </c>
       <c r="N98" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Bolderoll Slope","count":10}}</v>
       </c>
       <c r="O98" t="str">
         <v/>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B99" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C99" t="str">
         <v>Bolderoll Slope</v>
@@ -5046,10 +5046,10 @@
         <v>No</v>
       </c>
       <c r="M99" t="str">
-        <v/>
+        <v>Holm of Trials</v>
       </c>
       <c r="N99" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Bolderoll Slope","count":10}}</v>
       </c>
       <c r="O99" t="str">
         <v/>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B101" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C101" t="str">
         <v>Holm of Trials</v>
@@ -5140,10 +5140,10 @@
         <v>No</v>
       </c>
       <c r="M101" t="str">
-        <v/>
+        <v>Crossing Slope</v>
       </c>
       <c r="N101" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Holm of Trials","count":10}}</v>
       </c>
       <c r="O101" t="str">
         <v/>
@@ -5151,10 +5151,10 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C102" t="str">
         <v>Holm of Trials</v>
@@ -5187,10 +5187,10 @@
         <v>No</v>
       </c>
       <c r="M102" t="str">
-        <v/>
+        <v>Crossing Slope</v>
       </c>
       <c r="N102" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Holm of Trials","count":10}}</v>
       </c>
       <c r="O102" t="str">
         <v/>
@@ -5198,10 +5198,10 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C103" t="str">
         <v>Holm of Trials</v>
@@ -5234,10 +5234,10 @@
         <v>No</v>
       </c>
       <c r="M103" t="str">
-        <v/>
+        <v>Crossing Slope</v>
       </c>
       <c r="N103" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Holm of Trials","count":10}}</v>
       </c>
       <c r="O103" t="str">
         <v/>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C105" t="str">
         <v>Crossing Slope</v>
@@ -5328,10 +5328,10 @@
         <v>No</v>
       </c>
       <c r="M105" t="str">
-        <v/>
+        <v>Bathers' Lagoon</v>
       </c>
       <c r="N105" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Crossing Slope","count":10}}</v>
       </c>
       <c r="O105" t="str">
         <v/>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C106" t="str">
         <v>Crossing Slope</v>
@@ -5375,10 +5375,10 @@
         <v>No</v>
       </c>
       <c r="M106" t="str">
-        <v/>
+        <v>Bathers' Lagoon</v>
       </c>
       <c r="N106" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Crossing Slope","count":10}}</v>
       </c>
       <c r="O106" t="str">
         <v/>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C107" t="str">
         <v>Crossing Slope</v>
@@ -5422,10 +5422,10 @@
         <v>No</v>
       </c>
       <c r="M107" t="str">
-        <v/>
+        <v>Bathers' Lagoon</v>
       </c>
       <c r="N107" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Crossing Slope","count":10}}</v>
       </c>
       <c r="O107" t="str">
         <v/>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C108" t="str">
         <v>Crossing Slope</v>
@@ -5469,10 +5469,10 @@
         <v>No</v>
       </c>
       <c r="M108" t="str">
-        <v/>
+        <v>Bathers' Lagoon</v>
       </c>
       <c r="N108" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Crossing Slope","count":10}}</v>
       </c>
       <c r="O108" t="str">
         <v/>
@@ -5480,10 +5480,10 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C109" t="str">
         <v>Crossing Slope</v>
@@ -5516,10 +5516,10 @@
         <v>No</v>
       </c>
       <c r="M109" t="str">
-        <v/>
+        <v>Bathers' Lagoon</v>
       </c>
       <c r="N109" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Crossing Slope","count":10}}</v>
       </c>
       <c r="O109" t="str">
         <v/>
@@ -5527,10 +5527,10 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C110" t="str">
         <v>Crossing Slope</v>
@@ -5563,10 +5563,10 @@
         <v>No</v>
       </c>
       <c r="M110" t="str">
-        <v/>
+        <v>Bathers' Lagoon</v>
       </c>
       <c r="N110" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Crossing Slope","count":10}}</v>
       </c>
       <c r="O110" t="str">
         <v/>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C112" t="str">
         <v>Bathers' Lagoon</v>
@@ -5657,10 +5657,10 @@
         <v>No</v>
       </c>
       <c r="M112" t="str">
-        <v/>
+        <v>Castaway Shore</v>
       </c>
       <c r="N112" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Bathers' Lagoon","count":10}}</v>
       </c>
       <c r="O112" t="str">
         <v/>
@@ -5668,10 +5668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C113" t="str">
         <v>Bathers' Lagoon</v>
@@ -5704,10 +5704,10 @@
         <v>No</v>
       </c>
       <c r="M113" t="str">
-        <v/>
+        <v>Castaway Shore</v>
       </c>
       <c r="N113" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Bathers' Lagoon","count":10}}</v>
       </c>
       <c r="O113" t="str">
         <v/>
@@ -5715,10 +5715,10 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C114" t="str">
         <v>Bathers' Lagoon</v>
@@ -5751,10 +5751,10 @@
         <v>No</v>
       </c>
       <c r="M114" t="str">
-        <v/>
+        <v>Castaway Shore</v>
       </c>
       <c r="N114" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Bathers' Lagoon","count":10}}</v>
       </c>
       <c r="O114" t="str">
         <v/>
@@ -5809,10 +5809,10 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C116" t="str">
         <v>Castaway Shore</v>
@@ -5845,10 +5845,10 @@
         <v>No</v>
       </c>
       <c r="M116" t="str">
-        <v/>
+        <v>Deadwood Haunt</v>
       </c>
       <c r="N116" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Castaway Shore","count":10}}</v>
       </c>
       <c r="O116" t="str">
         <v/>
@@ -5856,10 +5856,10 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C117" t="str">
         <v>Castaway Shore</v>
@@ -5892,10 +5892,10 @@
         <v>No</v>
       </c>
       <c r="M117" t="str">
-        <v/>
+        <v>Deadwood Haunt</v>
       </c>
       <c r="N117" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Castaway Shore","count":10}}</v>
       </c>
       <c r="O117" t="str">
         <v/>
@@ -5950,10 +5950,10 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B119" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C119" t="str">
         <v>Deadwood Haunt</v>
@@ -5986,10 +5986,10 @@
         <v>No</v>
       </c>
       <c r="M119" t="str">
-        <v/>
+        <v>Gym - Arcanine</v>
       </c>
       <c r="N119" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deadwood Haunt","count":10}}</v>
       </c>
       <c r="O119" t="str">
         <v/>
@@ -5997,10 +5997,10 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B120" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C120" t="str">
         <v>Deadwood Haunt</v>
@@ -6033,10 +6033,10 @@
         <v>No</v>
       </c>
       <c r="M120" t="str">
-        <v/>
+        <v>Gym - Arcanine</v>
       </c>
       <c r="N120" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deadwood Haunt","count":10}}</v>
       </c>
       <c r="O120" t="str">
         <v/>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B121" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C121" t="str">
         <v>Deadwood Haunt</v>
@@ -6080,10 +6080,10 @@
         <v>No</v>
       </c>
       <c r="M121" t="str">
-        <v/>
+        <v>Gym - Arcanine</v>
       </c>
       <c r="N121" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Deadwood Haunt","count":10}}</v>
       </c>
       <c r="O121" t="str">
         <v/>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B124" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C124" t="str">
         <v>Veilstone Cape</v>
@@ -6221,10 +6221,10 @@
         <v>No</v>
       </c>
       <c r="M124" t="str">
-        <v/>
+        <v>Tranquility Cove</v>
       </c>
       <c r="N124" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Veilstone Cape","count":10}}</v>
       </c>
       <c r="O124" t="str">
         <v/>
@@ -6232,10 +6232,10 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B125" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C125" t="str">
         <v>Veilstone Cape</v>
@@ -6268,10 +6268,10 @@
         <v>No</v>
       </c>
       <c r="M125" t="str">
-        <v/>
+        <v>Tranquility Cove</v>
       </c>
       <c r="N125" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Veilstone Cape","count":10}}</v>
       </c>
       <c r="O125" t="str">
         <v/>
@@ -6279,10 +6279,10 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B126" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C126" t="str">
         <v>Veilstone Cape</v>
@@ -6315,10 +6315,10 @@
         <v>No</v>
       </c>
       <c r="M126" t="str">
-        <v/>
+        <v>Tranquility Cove</v>
       </c>
       <c r="N126" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Veilstone Cape","count":10}}</v>
       </c>
       <c r="O126" t="str">
         <v/>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B127" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C127" t="str">
         <v>Veilstone Cape</v>
@@ -6362,10 +6362,10 @@
         <v>No</v>
       </c>
       <c r="M127" t="str">
-        <v/>
+        <v>Tranquility Cove</v>
       </c>
       <c r="N127" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Veilstone Cape","count":10}}</v>
       </c>
       <c r="O127" t="str">
         <v/>
@@ -6420,10 +6420,10 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B129" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C129" t="str">
         <v>Tranquility Cove</v>
@@ -6456,10 +6456,10 @@
         <v>No</v>
       </c>
       <c r="M129" t="str">
-        <v/>
+        <v>Islespy Shore</v>
       </c>
       <c r="N129" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Tranquility Cove","count":10}}</v>
       </c>
       <c r="O129" t="str">
         <v/>
@@ -6467,10 +6467,10 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B130" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C130" t="str">
         <v>Tranquility Cove</v>
@@ -6503,10 +6503,10 @@
         <v>No</v>
       </c>
       <c r="M130" t="str">
-        <v/>
+        <v>Islespy Shore</v>
       </c>
       <c r="N130" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Tranquility Cove","count":10}}</v>
       </c>
       <c r="O130" t="str">
         <v/>
@@ -6514,10 +6514,10 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B131" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C131" t="str">
         <v>Tranquility Cove</v>
@@ -6550,10 +6550,10 @@
         <v>No</v>
       </c>
       <c r="M131" t="str">
-        <v/>
+        <v>Islespy Shore</v>
       </c>
       <c r="N131" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Tranquility Cove","count":10}}</v>
       </c>
       <c r="O131" t="str">
         <v/>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B132" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C132" t="str">
         <v>Tranquility Cove</v>
@@ -6597,10 +6597,10 @@
         <v>No</v>
       </c>
       <c r="M132" t="str">
-        <v/>
+        <v>Islespy Shore</v>
       </c>
       <c r="N132" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Tranquility Cove","count":10}}</v>
       </c>
       <c r="O132" t="str">
         <v/>
@@ -6655,10 +6655,10 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B134" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C134" t="str">
         <v>Islespy Shore</v>
@@ -6691,10 +6691,10 @@
         <v>No</v>
       </c>
       <c r="M134" t="str">
-        <v/>
+        <v>Firespit Island</v>
       </c>
       <c r="N134" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Islespy Shore","count":10}}</v>
       </c>
       <c r="O134" t="str">
         <v/>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B135" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C135" t="str">
         <v>Islespy Shore</v>
@@ -6738,10 +6738,10 @@
         <v>No</v>
       </c>
       <c r="M135" t="str">
-        <v/>
+        <v>Firespit Island</v>
       </c>
       <c r="N135" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Islespy Shore","count":10}}</v>
       </c>
       <c r="O135" t="str">
         <v/>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B136" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C136" t="str">
         <v>Islespy Shore</v>
@@ -6785,10 +6785,10 @@
         <v>No</v>
       </c>
       <c r="M136" t="str">
-        <v/>
+        <v>Firespit Island</v>
       </c>
       <c r="N136" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Islespy Shore","count":10}}</v>
       </c>
       <c r="O136" t="str">
         <v/>
@@ -6796,10 +6796,10 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B137" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C137" t="str">
         <v>Islespy Shore</v>
@@ -6832,10 +6832,10 @@
         <v>No</v>
       </c>
       <c r="M137" t="str">
-        <v/>
+        <v>Firespit Island</v>
       </c>
       <c r="N137" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Islespy Shore","count":10}}</v>
       </c>
       <c r="O137" t="str">
         <v/>
@@ -6843,10 +6843,10 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B138" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C138" t="str">
         <v>Islespy Shore</v>
@@ -6866,8 +6866,8 @@
       <c r="H138" s="1">
         <v>0.2</v>
       </c>
-      <c r="I138" t="str">
-        <v/>
+      <c r="I138" s="1">
+        <v>0.15</v>
       </c>
       <c r="J138" t="str">
         <v>Yes</v>
@@ -6879,10 +6879,10 @@
         <v>No</v>
       </c>
       <c r="M138" t="str">
-        <v/>
+        <v>Firespit Island</v>
       </c>
       <c r="N138" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Islespy Shore","count":10}}</v>
       </c>
       <c r="O138" t="str">
         <v/>
@@ -6937,10 +6937,10 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B140" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C140" t="str">
         <v>Firespit Island</v>
@@ -6973,10 +6973,10 @@
         <v>No</v>
       </c>
       <c r="M140" t="str">
-        <v/>
+        <v>Spring Path</v>
       </c>
       <c r="N140" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Firespit Island","count":10}}</v>
       </c>
       <c r="O140" t="str">
         <v/>
@@ -6984,10 +6984,10 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B141" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C141" t="str">
         <v>Firespit Island</v>
@@ -7020,10 +7020,10 @@
         <v>No</v>
       </c>
       <c r="M141" t="str">
-        <v/>
+        <v>Spring Path</v>
       </c>
       <c r="N141" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Firespit Island","count":10}}</v>
       </c>
       <c r="O141" t="str">
         <v/>
@@ -7031,10 +7031,10 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B142" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C142" t="str">
         <v>Firespit Island</v>
@@ -7067,10 +7067,10 @@
         <v>No</v>
       </c>
       <c r="M142" t="str">
-        <v/>
+        <v>Spring Path</v>
       </c>
       <c r="N142" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Firespit Island","count":10}}</v>
       </c>
       <c r="O142" t="str">
         <v/>
@@ -7078,10 +7078,10 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B143" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C143" t="str">
         <v>Firespit Island</v>
@@ -7114,10 +7114,10 @@
         <v>No</v>
       </c>
       <c r="M143" t="str">
-        <v/>
+        <v>Spring Path</v>
       </c>
       <c r="N143" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Firespit Island","count":10}}</v>
       </c>
       <c r="O143" t="str">
         <v/>
@@ -7172,10 +7172,10 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B145" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C145" t="str">
         <v>Spring Path</v>
@@ -7208,10 +7208,10 @@
         <v>No</v>
       </c>
       <c r="M145" t="str">
-        <v/>
+        <v>Celestica Trail</v>
       </c>
       <c r="N145" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Spring Path","count":10}}</v>
       </c>
       <c r="O145" t="str">
         <v/>
@@ -7219,10 +7219,10 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B146" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C146" t="str">
         <v>Spring Path</v>
@@ -7255,10 +7255,10 @@
         <v>No</v>
       </c>
       <c r="M146" t="str">
-        <v/>
+        <v>Celestica Trail</v>
       </c>
       <c r="N146" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Spring Path","count":10}}</v>
       </c>
       <c r="O146" t="str">
         <v/>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B147" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C147" t="str">
         <v>Spring Path</v>
@@ -7302,10 +7302,10 @@
         <v>No</v>
       </c>
       <c r="M147" t="str">
-        <v/>
+        <v>Celestica Trail</v>
       </c>
       <c r="N147" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Spring Path","count":10}}</v>
       </c>
       <c r="O147" t="str">
         <v/>
@@ -7360,10 +7360,10 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B149" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C149" t="str">
         <v>Celestica Trail</v>
@@ -7396,10 +7396,10 @@
         <v>No</v>
       </c>
       <c r="M149" t="str">
-        <v/>
+        <v>Celestica Ruins</v>
       </c>
       <c r="N149" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Celestica Trail","count":10}}</v>
       </c>
       <c r="O149" t="str">
         <v/>
@@ -7407,10 +7407,10 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B150" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C150" t="str">
         <v>Celestica Trail</v>
@@ -7443,10 +7443,10 @@
         <v>No</v>
       </c>
       <c r="M150" t="str">
-        <v/>
+        <v>Celestica Ruins</v>
       </c>
       <c r="N150" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Celestica Trail","count":10}}</v>
       </c>
       <c r="O150" t="str">
         <v/>
@@ -7454,10 +7454,10 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B151" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C151" t="str">
         <v>Celestica Trail</v>
@@ -7490,10 +7490,10 @@
         <v>No</v>
       </c>
       <c r="M151" t="str">
-        <v/>
+        <v>Celestica Ruins</v>
       </c>
       <c r="N151" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Celestica Trail","count":10}}</v>
       </c>
       <c r="O151" t="str">
         <v/>
@@ -7501,10 +7501,10 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B152" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C152" t="str">
         <v>Celestica Trail</v>
@@ -7537,10 +7537,10 @@
         <v>No</v>
       </c>
       <c r="M152" t="str">
-        <v/>
+        <v>Celestica Ruins</v>
       </c>
       <c r="N152" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Celestica Trail","count":10}}</v>
       </c>
       <c r="O152" t="str">
         <v/>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B154" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C154" t="str">
         <v>Celestica Ruins</v>
@@ -7631,10 +7631,10 @@
         <v>No</v>
       </c>
       <c r="M154" t="str">
-        <v/>
+        <v>Sacred Plaza</v>
       </c>
       <c r="N154" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Celestica Ruins","count":10}}</v>
       </c>
       <c r="O154" t="str">
         <v/>
@@ -7642,10 +7642,10 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B155" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C155" t="str">
         <v>Celestica Ruins</v>
@@ -7678,10 +7678,10 @@
         <v>No</v>
       </c>
       <c r="M155" t="str">
-        <v/>
+        <v>Sacred Plaza</v>
       </c>
       <c r="N155" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Celestica Ruins","count":10}}</v>
       </c>
       <c r="O155" t="str">
         <v/>
@@ -7689,10 +7689,10 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B156" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C156" t="str">
         <v>Celestica Ruins</v>
@@ -7725,10 +7725,10 @@
         <v>No</v>
       </c>
       <c r="M156" t="str">
-        <v/>
+        <v>Sacred Plaza</v>
       </c>
       <c r="N156" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Celestica Ruins","count":10}}</v>
       </c>
       <c r="O156" t="str">
         <v/>
@@ -7783,10 +7783,10 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B158" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C158" t="str">
         <v>Sacred Plaza</v>
@@ -7819,10 +7819,10 @@
         <v>No</v>
       </c>
       <c r="M158" t="str">
-        <v/>
+        <v>Stonetooth Rows</v>
       </c>
       <c r="N158" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Sacred Plaza","count":10}}</v>
       </c>
       <c r="O158" t="str">
         <v/>
@@ -7830,10 +7830,10 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B159" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C159" t="str">
         <v>Sacred Plaza</v>
@@ -7866,10 +7866,10 @@
         <v>No</v>
       </c>
       <c r="M159" t="str">
-        <v/>
+        <v>Stonetooth Rows</v>
       </c>
       <c r="N159" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Sacred Plaza","count":10}}</v>
       </c>
       <c r="O159" t="str">
         <v/>
@@ -7877,10 +7877,10 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B160" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C160" t="str">
         <v>Sacred Plaza</v>
@@ -7913,10 +7913,10 @@
         <v>No</v>
       </c>
       <c r="M160" t="str">
-        <v/>
+        <v>Stonetooth Rows</v>
       </c>
       <c r="N160" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Sacred Plaza","count":10}}</v>
       </c>
       <c r="O160" t="str">
         <v/>
@@ -7924,10 +7924,10 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B161" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C161" t="str">
         <v>Sacred Plaza</v>
@@ -7960,10 +7960,10 @@
         <v>No</v>
       </c>
       <c r="M161" t="str">
-        <v/>
+        <v>Stonetooth Rows</v>
       </c>
       <c r="N161" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Sacred Plaza","count":10}}</v>
       </c>
       <c r="O161" t="str">
         <v/>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B163" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C163" t="str">
         <v>Stonetooth Rows</v>
@@ -8054,10 +8054,10 @@
         <v>No</v>
       </c>
       <c r="M163" t="str">
-        <v/>
+        <v>Primeval Grotto</v>
       </c>
       <c r="N163" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Stonetooth Rows","count":10}}</v>
       </c>
       <c r="O163" t="str">
         <v/>
@@ -8065,10 +8065,10 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B164" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C164" t="str">
         <v>Stonetooth Rows</v>
@@ -8101,10 +8101,10 @@
         <v>No</v>
       </c>
       <c r="M164" t="str">
-        <v/>
+        <v>Primeval Grotto</v>
       </c>
       <c r="N164" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Stonetooth Rows","count":10}}</v>
       </c>
       <c r="O164" t="str">
         <v/>
@@ -8112,10 +8112,10 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B165" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C165" t="str">
         <v>Stonetooth Rows</v>
@@ -8148,10 +8148,10 @@
         <v>No</v>
       </c>
       <c r="M165" t="str">
-        <v/>
+        <v>Primeval Grotto</v>
       </c>
       <c r="N165" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Stonetooth Rows","count":10}}</v>
       </c>
       <c r="O165" t="str">
         <v/>
@@ -8159,10 +8159,10 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B166" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C166" t="str">
         <v>Stonetooth Rows</v>
@@ -8195,10 +8195,10 @@
         <v>No</v>
       </c>
       <c r="M166" t="str">
-        <v/>
+        <v>Primeval Grotto</v>
       </c>
       <c r="N166" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Stonetooth Rows","count":10}}</v>
       </c>
       <c r="O166" t="str">
         <v/>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B168" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C168" t="str">
         <v>Primeval Grotto</v>
@@ -8289,10 +8289,10 @@
         <v>No</v>
       </c>
       <c r="M168" t="str">
-        <v/>
+        <v>Gym - Electrode</v>
       </c>
       <c r="N168" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Primeval Grotto","count":10}}</v>
       </c>
       <c r="O168" t="str">
         <v/>
@@ -8300,10 +8300,10 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B169" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C169" t="str">
         <v>Primeval Grotto</v>
@@ -8336,10 +8336,10 @@
         <v>No</v>
       </c>
       <c r="M169" t="str">
-        <v/>
+        <v>Gym - Electrode</v>
       </c>
       <c r="N169" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Primeval Grotto","count":10}}</v>
       </c>
       <c r="O169" t="str">
         <v/>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B170" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C170" t="str">
         <v>Primeval Grotto</v>
@@ -8383,10 +8383,10 @@
         <v>No</v>
       </c>
       <c r="M170" t="str">
-        <v/>
+        <v>Gym - Electrode</v>
       </c>
       <c r="N170" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Primeval Grotto","count":10}}</v>
       </c>
       <c r="O170" t="str">
         <v/>
@@ -8394,10 +8394,10 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B171" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C171" t="str">
         <v>Primeval Grotto</v>
@@ -8430,10 +8430,10 @@
         <v>No</v>
       </c>
       <c r="M171" t="str">
-        <v/>
+        <v>Gym - Electrode</v>
       </c>
       <c r="N171" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Primeval Grotto","count":10}}</v>
       </c>
       <c r="O171" t="str">
         <v/>
@@ -8441,10 +8441,10 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B172" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C172" t="str">
         <v>Primeval Grotto</v>
@@ -8464,8 +8464,8 @@
       <c r="H172" s="1">
         <v>0.2</v>
       </c>
-      <c r="I172" t="str">
-        <v/>
+      <c r="I172" s="1">
+        <v>0.15</v>
       </c>
       <c r="J172" t="str">
         <v>Yes</v>
@@ -8477,10 +8477,10 @@
         <v>No</v>
       </c>
       <c r="M172" t="str">
-        <v/>
+        <v>Gym - Electrode</v>
       </c>
       <c r="N172" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Primeval Grotto","count":10}}</v>
       </c>
       <c r="O172" t="str">
         <v/>
@@ -8582,10 +8582,10 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B175" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="C175" t="str">
         <v>Clamberclaw Cliffs</v>
@@ -8618,10 +8618,10 @@
         <v>No</v>
       </c>
       <c r="M175" t="str">
-        <v/>
+        <v>Coronet Highlands</v>
       </c>
       <c r="N175" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Clamberclaw Cliffs","count":10}}</v>
       </c>
       <c r="O175" t="str">
         <v/>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B176" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="C176" t="str">
         <v>Clamberclaw Cliffs</v>
@@ -8665,10 +8665,10 @@
         <v>No</v>
       </c>
       <c r="M176" t="str">
-        <v/>
+        <v>Coronet Highlands</v>
       </c>
       <c r="N176" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Clamberclaw Cliffs","count":10}}</v>
       </c>
       <c r="O176" t="str">
         <v/>
@@ -8676,10 +8676,10 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B177" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="C177" t="str">
         <v>Clamberclaw Cliffs</v>
@@ -8712,10 +8712,10 @@
         <v>No</v>
       </c>
       <c r="M177" t="str">
-        <v/>
+        <v>Coronet Highlands</v>
       </c>
       <c r="N177" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Clamberclaw Cliffs","count":10}}</v>
       </c>
       <c r="O177" t="str">
         <v/>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="B179" t="str">
-        <v/>
+        <v>Challenge 39</v>
       </c>
       <c r="C179" t="str">
         <v>Coronet Highlands</v>
@@ -8806,10 +8806,10 @@
         <v>No</v>
       </c>
       <c r="M179" t="str">
-        <v/>
+        <v>Fabled Spring</v>
       </c>
       <c r="N179" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Coronet Highlands","count":10}}</v>
       </c>
       <c r="O179" t="str">
         <v/>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="B180" t="str">
-        <v/>
+        <v>Challenge 39</v>
       </c>
       <c r="C180" t="str">
         <v>Coronet Highlands</v>
@@ -8853,10 +8853,10 @@
         <v>No</v>
       </c>
       <c r="M180" t="str">
-        <v/>
+        <v>Fabled Spring</v>
       </c>
       <c r="N180" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Coronet Highlands","count":10}}</v>
       </c>
       <c r="O180" t="str">
         <v/>
@@ -8911,10 +8911,10 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v/>
+        <v>Challenge 39</v>
       </c>
       <c r="B182" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="C182" t="str">
         <v>Fabled Spring</v>
@@ -8947,10 +8947,10 @@
         <v>No</v>
       </c>
       <c r="M182" t="str">
-        <v/>
+        <v>Whiteout Valley</v>
       </c>
       <c r="N182" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Fabled Spring","count":10}}</v>
       </c>
       <c r="O182" t="str">
         <v/>
@@ -8958,10 +8958,10 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v/>
+        <v>Challenge 39</v>
       </c>
       <c r="B183" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="C183" t="str">
         <v>Fabled Spring</v>
@@ -8994,10 +8994,10 @@
         <v>No</v>
       </c>
       <c r="M183" t="str">
-        <v/>
+        <v>Whiteout Valley</v>
       </c>
       <c r="N183" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Fabled Spring","count":10}}</v>
       </c>
       <c r="O183" t="str">
         <v/>
@@ -9005,10 +9005,10 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v/>
+        <v>Challenge 39</v>
       </c>
       <c r="B184" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="C184" t="str">
         <v>Fabled Spring</v>
@@ -9041,10 +9041,10 @@
         <v>No</v>
       </c>
       <c r="M184" t="str">
-        <v/>
+        <v>Whiteout Valley</v>
       </c>
       <c r="N184" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Fabled Spring","count":10}}</v>
       </c>
       <c r="O184" t="str">
         <v/>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="B186" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="C186" t="str">
         <v>Whiteout Valley</v>
@@ -9135,10 +9135,10 @@
         <v>No</v>
       </c>
       <c r="M186" t="str">
-        <v/>
+        <v>Bonechill Wastes North</v>
       </c>
       <c r="N186" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Whiteout Valley","count":10}}</v>
       </c>
       <c r="O186" t="str">
         <v/>
@@ -9146,10 +9146,10 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="B187" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="C187" t="str">
         <v>Whiteout Valley</v>
@@ -9182,10 +9182,10 @@
         <v>No</v>
       </c>
       <c r="M187" t="str">
-        <v/>
+        <v>Bonechill Wastes North</v>
       </c>
       <c r="N187" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Whiteout Valley","count":10}}</v>
       </c>
       <c r="O187" t="str">
         <v/>
@@ -9240,10 +9240,10 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B189" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="C189" t="str">
         <v>Bonechill Wastes North</v>
@@ -9276,10 +9276,10 @@
         <v>No</v>
       </c>
       <c r="M189" t="str">
-        <v/>
+        <v>Bonechill Wastes South</v>
       </c>
       <c r="N189" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Bonechill Wastes North","count":10}}</v>
       </c>
       <c r="O189" t="str">
         <v/>
@@ -9287,10 +9287,10 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B190" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="C190" t="str">
         <v>Bonechill Wastes North</v>
@@ -9323,10 +9323,10 @@
         <v>No</v>
       </c>
       <c r="M190" t="str">
-        <v/>
+        <v>Bonechill Wastes South</v>
       </c>
       <c r="N190" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Bonechill Wastes North","count":10}}</v>
       </c>
       <c r="O190" t="str">
         <v/>
@@ -9334,10 +9334,10 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B191" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="C191" t="str">
         <v>Bonechill Wastes North</v>
@@ -9370,10 +9370,10 @@
         <v>No</v>
       </c>
       <c r="M191" t="str">
-        <v/>
+        <v>Bonechill Wastes South</v>
       </c>
       <c r="N191" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Bonechill Wastes North","count":10}}</v>
       </c>
       <c r="O191" t="str">
         <v/>
@@ -9428,10 +9428,10 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B193" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C193" t="str">
         <v>Bonechill Wastes South</v>
@@ -9464,10 +9464,10 @@
         <v>No</v>
       </c>
       <c r="M193" t="str">
-        <v/>
+        <v>Arena's Approach</v>
       </c>
       <c r="N193" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Bonechill Wastes South","count":10}}</v>
       </c>
       <c r="O193" t="str">
         <v/>
@@ -9475,10 +9475,10 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B194" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C194" t="str">
         <v>Bonechill Wastes South</v>
@@ -9511,10 +9511,10 @@
         <v>No</v>
       </c>
       <c r="M194" t="str">
-        <v/>
+        <v>Arena's Approach</v>
       </c>
       <c r="N194" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Bonechill Wastes South","count":10}}</v>
       </c>
       <c r="O194" t="str">
         <v/>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B195" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C195" t="str">
         <v>Bonechill Wastes South</v>
@@ -9558,10 +9558,10 @@
         <v>No</v>
       </c>
       <c r="M195" t="str">
-        <v/>
+        <v>Arena's Approach</v>
       </c>
       <c r="N195" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Bonechill Wastes South","count":10}}</v>
       </c>
       <c r="O195" t="str">
         <v/>
@@ -9616,10 +9616,10 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B197" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C197" t="str">
         <v>Arena's Approach</v>
@@ -9652,10 +9652,10 @@
         <v>No</v>
       </c>
       <c r="M197" t="str">
-        <v/>
+        <v>Glacier Terrace</v>
       </c>
       <c r="N197" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Arena's Approach","count":10}}</v>
       </c>
       <c r="O197" t="str">
         <v/>
@@ -9663,10 +9663,10 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B198" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C198" t="str">
         <v>Arena's Approach</v>
@@ -9699,10 +9699,10 @@
         <v>No</v>
       </c>
       <c r="M198" t="str">
-        <v/>
+        <v>Glacier Terrace</v>
       </c>
       <c r="N198" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Arena's Approach","count":10}}</v>
       </c>
       <c r="O198" t="str">
         <v/>
@@ -9710,10 +9710,10 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B199" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C199" t="str">
         <v>Arena's Approach</v>
@@ -9746,10 +9746,10 @@
         <v>No</v>
       </c>
       <c r="M199" t="str">
-        <v/>
+        <v>Glacier Terrace</v>
       </c>
       <c r="N199" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Arena's Approach","count":10}}</v>
       </c>
       <c r="O199" t="str">
         <v/>
@@ -9757,10 +9757,10 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B200" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C200" t="str">
         <v>Arena's Approach</v>
@@ -9793,10 +9793,10 @@
         <v>No</v>
       </c>
       <c r="M200" t="str">
-        <v/>
+        <v>Glacier Terrace</v>
       </c>
       <c r="N200" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Arena's Approach","count":10}}</v>
       </c>
       <c r="O200" t="str">
         <v/>
@@ -9804,10 +9804,10 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B201" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C201" t="str">
         <v>Arena's Approach</v>
@@ -9840,10 +9840,10 @@
         <v>No</v>
       </c>
       <c r="M201" t="str">
-        <v/>
+        <v>Glacier Terrace</v>
       </c>
       <c r="N201" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Arena's Approach","count":10}}</v>
       </c>
       <c r="O201" t="str">
         <v/>
@@ -9851,10 +9851,10 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B202" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C202" t="str">
         <v>Arena's Approach</v>
@@ -9887,10 +9887,10 @@
         <v>No</v>
       </c>
       <c r="M202" t="str">
-        <v/>
+        <v>Glacier Terrace</v>
       </c>
       <c r="N202" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Arena's Approach","count":10}}</v>
       </c>
       <c r="O202" t="str">
         <v/>
@@ -9945,10 +9945,10 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B204" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="C204" t="str">
         <v>Glacier Terrace</v>
@@ -9981,10 +9981,10 @@
         <v>No</v>
       </c>
       <c r="M204" t="str">
-        <v/>
+        <v>Heart's Crag</v>
       </c>
       <c r="N204" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Glacier Terrace","count":10}}</v>
       </c>
       <c r="O204" t="str">
         <v/>
@@ -9992,10 +9992,10 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B205" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="C205" t="str">
         <v>Glacier Terrace</v>
@@ -10028,10 +10028,10 @@
         <v>No</v>
       </c>
       <c r="M205" t="str">
-        <v/>
+        <v>Heart's Crag</v>
       </c>
       <c r="N205" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Glacier Terrace","count":10}}</v>
       </c>
       <c r="O205" t="str">
         <v/>
@@ -10086,10 +10086,10 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B207" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C207" t="str">
         <v>Heart's Crag</v>
@@ -10122,10 +10122,10 @@
         <v>No</v>
       </c>
       <c r="M207" t="str">
-        <v/>
+        <v>Snowpoint Temple</v>
       </c>
       <c r="N207" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Heart's Crag","count":10}}</v>
       </c>
       <c r="O207" t="str">
         <v/>
@@ -10133,10 +10133,10 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B208" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C208" t="str">
         <v>Heart's Crag</v>
@@ -10169,10 +10169,10 @@
         <v>No</v>
       </c>
       <c r="M208" t="str">
-        <v/>
+        <v>Snowpoint Temple</v>
       </c>
       <c r="N208" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Heart's Crag","count":10}}</v>
       </c>
       <c r="O208" t="str">
         <v/>
@@ -10180,10 +10180,10 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B209" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C209" t="str">
         <v>Heart's Crag</v>
@@ -10216,10 +10216,10 @@
         <v>No</v>
       </c>
       <c r="M209" t="str">
-        <v/>
+        <v>Snowpoint Temple</v>
       </c>
       <c r="N209" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Heart's Crag","count":10}}</v>
       </c>
       <c r="O209" t="str">
         <v/>
@@ -10274,10 +10274,10 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="B211" t="str">
-        <v/>
+        <v>Challenge 47</v>
       </c>
       <c r="C211" t="str">
         <v>Snowpoint Temple</v>
@@ -10310,10 +10310,10 @@
         <v>No</v>
       </c>
       <c r="M211" t="str">
-        <v/>
+        <v>Gym - Avalugg</v>
       </c>
       <c r="N211" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Snowpoint Temple","count":10}}</v>
       </c>
       <c r="O211" t="str">
         <v/>
@@ -10321,10 +10321,10 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="B212" t="str">
-        <v/>
+        <v>Challenge 47</v>
       </c>
       <c r="C212" t="str">
         <v>Snowpoint Temple</v>
@@ -10357,10 +10357,10 @@
         <v>No</v>
       </c>
       <c r="M212" t="str">
-        <v/>
+        <v>Gym - Avalugg</v>
       </c>
       <c r="N212" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Snowpoint Temple","count":10}}</v>
       </c>
       <c r="O212" t="str">
         <v/>
@@ -10368,10 +10368,10 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="B213" t="str">
-        <v/>
+        <v>Challenge 47</v>
       </c>
       <c r="C213" t="str">
         <v>Snowpoint Temple</v>
@@ -10404,10 +10404,10 @@
         <v>No</v>
       </c>
       <c r="M213" t="str">
-        <v/>
+        <v>Gym - Avalugg</v>
       </c>
       <c r="N213" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Snowpoint Temple","count":10}}</v>
       </c>
       <c r="O213" t="str">
         <v/>
@@ -10556,10 +10556,10 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B217" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="C217" t="str">
         <v>Obsidian Fieldlands Fishing Spot</v>
@@ -10592,10 +10592,10 @@
         <v>No</v>
       </c>
       <c r="M217" t="str">
-        <v/>
+        <v>Cobalt Coastlands Fishing Spot</v>
       </c>
       <c r="N217" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Obsidian Fieldlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O217" t="str">
         <v/>
@@ -10603,10 +10603,10 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B218" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="C218" t="str">
         <v>Obsidian Fieldlands Fishing Spot</v>
@@ -10639,10 +10639,10 @@
         <v>No</v>
       </c>
       <c r="M218" t="str">
-        <v/>
+        <v>Cobalt Coastlands Fishing Spot</v>
       </c>
       <c r="N218" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Obsidian Fieldlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O218" t="str">
         <v/>
@@ -10650,10 +10650,10 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B219" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="C219" t="str">
         <v>Obsidian Fieldlands Fishing Spot</v>
@@ -10686,10 +10686,10 @@
         <v>No</v>
       </c>
       <c r="M219" t="str">
-        <v/>
+        <v>Cobalt Coastlands Fishing Spot</v>
       </c>
       <c r="N219" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Obsidian Fieldlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O219" t="str">
         <v/>
@@ -10697,10 +10697,10 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B220" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="C220" t="str">
         <v>Obsidian Fieldlands Fishing Spot</v>
@@ -10733,10 +10733,10 @@
         <v>No</v>
       </c>
       <c r="M220" t="str">
-        <v/>
+        <v>Cobalt Coastlands Fishing Spot</v>
       </c>
       <c r="N220" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Obsidian Fieldlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O220" t="str">
         <v/>
@@ -10744,10 +10744,10 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B221" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="C221" t="str">
         <v>Obsidian Fieldlands Fishing Spot</v>
@@ -10767,8 +10767,8 @@
       <c r="H221" s="1">
         <v>0.2</v>
       </c>
-      <c r="I221" t="str">
-        <v/>
+      <c r="I221" s="1">
+        <v>0.15</v>
       </c>
       <c r="J221" t="str">
         <v/>
@@ -10780,10 +10780,10 @@
         <v>No</v>
       </c>
       <c r="M221" t="str">
-        <v/>
+        <v>Cobalt Coastlands Fishing Spot</v>
       </c>
       <c r="N221" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Obsidian Fieldlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O221" t="str">
         <v/>
@@ -10838,10 +10838,10 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B223" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="C223" t="str">
         <v>Cobalt Coastlands Fishing Spot</v>
@@ -10874,10 +10874,10 @@
         <v>No</v>
       </c>
       <c r="M223" t="str">
-        <v/>
+        <v>Crimson Mirelands Fishing Spot</v>
       </c>
       <c r="N223" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Cobalt Coastlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O223" t="str">
         <v/>
@@ -10885,10 +10885,10 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B224" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="C224" t="str">
         <v>Cobalt Coastlands Fishing Spot</v>
@@ -10921,10 +10921,10 @@
         <v>No</v>
       </c>
       <c r="M224" t="str">
-        <v/>
+        <v>Crimson Mirelands Fishing Spot</v>
       </c>
       <c r="N224" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Cobalt Coastlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O224" t="str">
         <v/>
@@ -10932,10 +10932,10 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B225" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="C225" t="str">
         <v>Cobalt Coastlands Fishing Spot</v>
@@ -10968,10 +10968,10 @@
         <v>No</v>
       </c>
       <c r="M225" t="str">
-        <v/>
+        <v>Crimson Mirelands Fishing Spot</v>
       </c>
       <c r="N225" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Cobalt Coastlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O225" t="str">
         <v/>
@@ -10979,10 +10979,10 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B226" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="C226" t="str">
         <v>Cobalt Coastlands Fishing Spot</v>
@@ -11015,10 +11015,10 @@
         <v>No</v>
       </c>
       <c r="M226" t="str">
-        <v/>
+        <v>Crimson Mirelands Fishing Spot</v>
       </c>
       <c r="N226" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Cobalt Coastlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O226" t="str">
         <v/>
@@ -11073,10 +11073,10 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B228" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C228" t="str">
         <v>Crimson Mirelands Fishing Spot</v>
@@ -11109,10 +11109,10 @@
         <v>No</v>
       </c>
       <c r="M228" t="str">
-        <v/>
+        <v>Ginkgo Landing</v>
       </c>
       <c r="N228" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Crimson Mirelands Fishing Spot","count":10}}</v>
       </c>
       <c r="O228" t="str">
         <v/>
@@ -11120,10 +11120,10 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B229" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C229" t="str">
         <v>Crimson Mirelands Fishing Spot</v>
@@ -11156,10 +11156,10 @@
         <v>No</v>
       </c>
       <c r="M229" t="str">
-        <v/>
+        <v>Ginkgo Landing</v>
       </c>
       <c r="N229" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Crimson Mirelands Fishing Spot","count":10}}</v>
       </c>
       <c r="O229" t="str">
         <v/>
@@ -11167,10 +11167,10 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B230" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C230" t="str">
         <v>Crimson Mirelands Fishing Spot</v>
@@ -11203,10 +11203,10 @@
         <v>No</v>
       </c>
       <c r="M230" t="str">
-        <v/>
+        <v>Ginkgo Landing</v>
       </c>
       <c r="N230" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Crimson Mirelands Fishing Spot","count":10}}</v>
       </c>
       <c r="O230" t="str">
         <v/>
@@ -11261,10 +11261,10 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B232" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C232" t="str">
         <v>Ginkgo Landing</v>
@@ -11297,10 +11297,10 @@
         <v>No</v>
       </c>
       <c r="M232" t="str">
-        <v/>
+        <v>Shrouded Ruins</v>
       </c>
       <c r="N232" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Ginkgo Landing","count":10}}</v>
       </c>
       <c r="O232" t="str">
         <v/>
@@ -11308,10 +11308,10 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B233" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C233" t="str">
         <v>Ginkgo Landing</v>
@@ -11344,10 +11344,10 @@
         <v>No</v>
       </c>
       <c r="M233" t="str">
-        <v/>
+        <v>Shrouded Ruins</v>
       </c>
       <c r="N233" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Ginkgo Landing","count":10}}</v>
       </c>
       <c r="O233" t="str">
         <v/>
@@ -11355,10 +11355,10 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B234" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C234" t="str">
         <v>Ginkgo Landing</v>
@@ -11391,10 +11391,10 @@
         <v>No</v>
       </c>
       <c r="M234" t="str">
-        <v/>
+        <v>Shrouded Ruins</v>
       </c>
       <c r="N234" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Ginkgo Landing","count":10}}</v>
       </c>
       <c r="O234" t="str">
         <v/>
@@ -11449,10 +11449,10 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B236" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="C236" t="str">
         <v>Shrouded Ruins</v>
@@ -11485,10 +11485,10 @@
         <v>No</v>
       </c>
       <c r="M236" t="str">
-        <v/>
+        <v>Sandgem Flats South</v>
       </c>
       <c r="N236" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Shrouded Ruins","count":10}}</v>
       </c>
       <c r="O236" t="str">
         <v/>
@@ -11496,10 +11496,10 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B237" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="C237" t="str">
         <v>Shrouded Ruins</v>
@@ -11532,10 +11532,10 @@
         <v>No</v>
       </c>
       <c r="M237" t="str">
-        <v/>
+        <v>Sandgem Flats South</v>
       </c>
       <c r="N237" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Shrouded Ruins","count":10}}</v>
       </c>
       <c r="O237" t="str">
         <v/>
@@ -11543,10 +11543,10 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B238" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="C238" t="str">
         <v>Shrouded Ruins</v>
@@ -11579,10 +11579,10 @@
         <v>No</v>
       </c>
       <c r="M238" t="str">
-        <v/>
+        <v>Sandgem Flats South</v>
       </c>
       <c r="N238" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Shrouded Ruins","count":10}}</v>
       </c>
       <c r="O238" t="str">
         <v/>
@@ -11590,10 +11590,10 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B239" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="C239" t="str">
         <v>Shrouded Ruins</v>
@@ -11626,10 +11626,10 @@
         <v>No</v>
       </c>
       <c r="M239" t="str">
-        <v/>
+        <v>Sandgem Flats South</v>
       </c>
       <c r="N239" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Shrouded Ruins","count":10}}</v>
       </c>
       <c r="O239" t="str">
         <v/>
@@ -11637,10 +11637,10 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B240" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="C240" t="str">
         <v>Shrouded Ruins</v>
@@ -11660,8 +11660,8 @@
       <c r="H240" s="1">
         <v>0.2</v>
       </c>
-      <c r="I240" t="str">
-        <v/>
+      <c r="I240" s="1">
+        <v>0.15</v>
       </c>
       <c r="J240" t="str">
         <v>Yes</v>
@@ -11673,10 +11673,10 @@
         <v>No</v>
       </c>
       <c r="M240" t="str">
-        <v/>
+        <v>Sandgem Flats South</v>
       </c>
       <c r="N240" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Shrouded Ruins","count":10}}</v>
       </c>
       <c r="O240" t="str">
         <v/>
@@ -11731,10 +11731,10 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="B242" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="C242" t="str">
         <v>Sandgem Flats South</v>
@@ -11767,10 +11767,10 @@
         <v>No</v>
       </c>
       <c r="M242" t="str">
-        <v/>
+        <v>Ramanas Island South</v>
       </c>
       <c r="N242" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Sandgem Flats South","count":10}}</v>
       </c>
       <c r="O242" t="str">
         <v/>
@@ -11778,10 +11778,10 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="B243" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="C243" t="str">
         <v>Sandgem Flats South</v>
@@ -11814,10 +11814,10 @@
         <v>No</v>
       </c>
       <c r="M243" t="str">
-        <v/>
+        <v>Ramanas Island South</v>
       </c>
       <c r="N243" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Sandgem Flats South","count":10}}</v>
       </c>
       <c r="O243" t="str">
         <v/>
@@ -11872,10 +11872,10 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="B245" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="C245" t="str">
         <v>Ramanas Island South</v>
@@ -11908,10 +11908,10 @@
         <v>No</v>
       </c>
       <c r="M245" t="str">
-        <v/>
+        <v>Sandgem Flats North</v>
       </c>
       <c r="N245" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Ramanas Island South","count":10}}</v>
       </c>
       <c r="O245" t="str">
         <v/>
@@ -11919,10 +11919,10 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="B246" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="C246" t="str">
         <v>Ramanas Island South</v>
@@ -11955,10 +11955,10 @@
         <v>No</v>
       </c>
       <c r="M246" t="str">
-        <v/>
+        <v>Sandgem Flats North</v>
       </c>
       <c r="N246" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Ramanas Island South","count":10}}</v>
       </c>
       <c r="O246" t="str">
         <v/>
@@ -11966,10 +11966,10 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="B247" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="C247" t="str">
         <v>Ramanas Island South</v>
@@ -12002,10 +12002,10 @@
         <v>No</v>
       </c>
       <c r="M247" t="str">
-        <v/>
+        <v>Sandgem Flats North</v>
       </c>
       <c r="N247" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Ramanas Island South","count":10}}</v>
       </c>
       <c r="O247" t="str">
         <v/>
@@ -12060,7 +12060,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="B249" t="str">
         <v/>
@@ -12107,7 +12107,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="B250" t="str">
         <v/>
@@ -12154,7 +12154,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="B251" t="str">
         <v/>
@@ -12248,10 +12248,10 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B253" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C253" t="str">
         <v>Coronet Highlands Fishing Spot</v>
@@ -12284,10 +12284,10 @@
         <v>No</v>
       </c>
       <c r="M253" t="str">
-        <v/>
+        <v>Cloudpool Ridge North</v>
       </c>
       <c r="N253" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Coronet Highlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O253" t="str">
         <v/>
@@ -12295,10 +12295,10 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B254" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C254" t="str">
         <v>Coronet Highlands Fishing Spot</v>
@@ -12331,10 +12331,10 @@
         <v>No</v>
       </c>
       <c r="M254" t="str">
-        <v/>
+        <v>Cloudpool Ridge North</v>
       </c>
       <c r="N254" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Coronet Highlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O254" t="str">
         <v/>
@@ -12342,10 +12342,10 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B255" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C255" t="str">
         <v>Coronet Highlands Fishing Spot</v>
@@ -12378,10 +12378,10 @@
         <v>No</v>
       </c>
       <c r="M255" t="str">
-        <v/>
+        <v>Cloudpool Ridge North</v>
       </c>
       <c r="N255" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Coronet Highlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O255" t="str">
         <v/>
@@ -12389,10 +12389,10 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B256" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C256" t="str">
         <v>Coronet Highlands Fishing Spot</v>
@@ -12425,10 +12425,10 @@
         <v>No</v>
       </c>
       <c r="M256" t="str">
-        <v/>
+        <v>Cloudpool Ridge North</v>
       </c>
       <c r="N256" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Coronet Highlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O256" t="str">
         <v/>
@@ -12436,10 +12436,10 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B257" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C257" t="str">
         <v>Coronet Highlands Fishing Spot</v>
@@ -12472,10 +12472,10 @@
         <v>No</v>
       </c>
       <c r="M257" t="str">
-        <v/>
+        <v>Cloudpool Ridge North</v>
       </c>
       <c r="N257" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Coronet Highlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O257" t="str">
         <v/>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B258" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C258" t="str">
         <v>Coronet Highlands Fishing Spot</v>
@@ -12519,10 +12519,10 @@
         <v>No</v>
       </c>
       <c r="M258" t="str">
-        <v/>
+        <v>Cloudpool Ridge North</v>
       </c>
       <c r="N258" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Coronet Highlands Fishing Spot","count":10}}</v>
       </c>
       <c r="O258" t="str">
         <v/>
@@ -12577,10 +12577,10 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B260" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="C260" t="str">
         <v>Cloudpool Ridge North</v>
@@ -12613,10 +12613,10 @@
         <v>No</v>
       </c>
       <c r="M260" t="str">
-        <v/>
+        <v>Cloudpool Ridge South</v>
       </c>
       <c r="N260" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Cloudpool Ridge North","count":10}}</v>
       </c>
       <c r="O260" t="str">
         <v/>
@@ -12624,10 +12624,10 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B261" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="C261" t="str">
         <v>Cloudpool Ridge North</v>
@@ -12660,10 +12660,10 @@
         <v>No</v>
       </c>
       <c r="M261" t="str">
-        <v/>
+        <v>Cloudpool Ridge South</v>
       </c>
       <c r="N261" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Cloudpool Ridge North","count":10}}</v>
       </c>
       <c r="O261" t="str">
         <v/>
@@ -12671,10 +12671,10 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B262" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="C262" t="str">
         <v>Cloudpool Ridge North</v>
@@ -12707,10 +12707,10 @@
         <v>No</v>
       </c>
       <c r="M262" t="str">
-        <v/>
+        <v>Cloudpool Ridge South</v>
       </c>
       <c r="N262" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Cloudpool Ridge North","count":10}}</v>
       </c>
       <c r="O262" t="str">
         <v/>
@@ -12765,10 +12765,10 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B264" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="C264" t="str">
         <v>Cloudpool Ridge South</v>
@@ -12801,10 +12801,10 @@
         <v>No</v>
       </c>
       <c r="M264" t="str">
-        <v/>
+        <v>Space-Time Distortion</v>
       </c>
       <c r="N264" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Cloudpool Ridge South","count":10}}</v>
       </c>
       <c r="O264" t="str">
         <v/>
@@ -12812,10 +12812,10 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B265" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="C265" t="str">
         <v>Cloudpool Ridge South</v>
@@ -12848,10 +12848,10 @@
         <v>No</v>
       </c>
       <c r="M265" t="str">
-        <v/>
+        <v>Space-Time Distortion</v>
       </c>
       <c r="N265" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Cloudpool Ridge South","count":10}}</v>
       </c>
       <c r="O265" t="str">
         <v/>
@@ -12906,7 +12906,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B267" t="str">
         <v/>
@@ -12953,7 +12953,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B268" t="str">
         <v/>
@@ -13000,7 +13000,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B269" t="str">
         <v/>
@@ -13047,7 +13047,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B270" t="str">
         <v/>
@@ -13094,7 +13094,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B271" t="str">
         <v/>
@@ -13141,7 +13141,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B272" t="str">
         <v/>
@@ -13188,7 +13188,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B273" t="str">
         <v/>
@@ -13235,7 +13235,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B274" t="str">
         <v/>
@@ -13282,7 +13282,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B275" t="str">
         <v/>
@@ -13329,7 +13329,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B276" t="str">
         <v/>
@@ -13376,7 +13376,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B277" t="str">
         <v/>
@@ -13423,7 +13423,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B278" t="str">
         <v/>
@@ -13470,7 +13470,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B279" t="str">
         <v/>
@@ -13517,7 +13517,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B280" t="str">
         <v/>
@@ -13564,7 +13564,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B281" t="str">
         <v/>
@@ -13611,7 +13611,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B282" t="str">
         <v/>
@@ -13658,7 +13658,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B283" t="str">
         <v/>
@@ -13705,7 +13705,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B284" t="str">
         <v/>
@@ -13752,7 +13752,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B285" t="str">
         <v/>
@@ -13799,7 +13799,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B286" t="str">
         <v/>
@@ -13846,7 +13846,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B287" t="str">
         <v/>
@@ -13893,7 +13893,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B288" t="str">
         <v/>
@@ -13940,7 +13940,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B289" t="str">
         <v/>
@@ -13987,7 +13987,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B290" t="str">
         <v/>
@@ -14034,7 +14034,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B291" t="str">
         <v/>
@@ -14081,7 +14081,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B292" t="str">
         <v/>
@@ -14128,7 +14128,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B293" t="str">
         <v/>
@@ -14175,7 +14175,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B294" t="str">
         <v/>
@@ -14222,7 +14222,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B295" t="str">
         <v/>
@@ -14269,7 +14269,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B296" t="str">
         <v/>
@@ -14316,7 +14316,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B297" t="str">
         <v/>
@@ -14363,7 +14363,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B298" t="str">
         <v/>
@@ -14410,7 +14410,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B299" t="str">
         <v/>
@@ -14457,7 +14457,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B300" t="str">
         <v/>
@@ -14504,7 +14504,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B301" t="str">
         <v/>
@@ -14551,7 +14551,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B302" t="str">
         <v/>
@@ -14598,7 +14598,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B303" t="str">
         <v/>
@@ -14645,7 +14645,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B304" t="str">
         <v/>
@@ -14692,7 +14692,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B305" t="str">
         <v/>
@@ -14739,7 +14739,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B306" t="str">
         <v/>
@@ -14786,7 +14786,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B307" t="str">
         <v/>
@@ -14809,8 +14809,8 @@
       <c r="H307" s="1">
         <v>0.18</v>
       </c>
-      <c r="I307" s="1">
-        <v>0.023809523809523808</v>
+      <c r="I307" t="str">
+        <v/>
       </c>
       <c r="J307" t="str">
         <v>Yes</v>
@@ -14880,10 +14880,10 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B309" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="C309" t="str">
         <v>Wayward Cave</v>
@@ -14916,10 +14916,10 @@
         <v>No</v>
       </c>
       <c r="M309" t="str">
-        <v/>
+        <v>Seagrass Haven</v>
       </c>
       <c r="N309" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Wayward Cave","count":10}}</v>
       </c>
       <c r="O309" t="str">
         <v/>
@@ -14927,10 +14927,10 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B310" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="C310" t="str">
         <v>Wayward Cave</v>
@@ -14963,10 +14963,10 @@
         <v>No</v>
       </c>
       <c r="M310" t="str">
-        <v/>
+        <v>Seagrass Haven</v>
       </c>
       <c r="N310" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Wayward Cave","count":10}}</v>
       </c>
       <c r="O310" t="str">
         <v/>
@@ -14974,10 +14974,10 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B311" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="C311" t="str">
         <v>Wayward Cave</v>
@@ -15010,10 +15010,10 @@
         <v>No</v>
       </c>
       <c r="M311" t="str">
-        <v/>
+        <v>Seagrass Haven</v>
       </c>
       <c r="N311" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Wayward Cave","count":10}}</v>
       </c>
       <c r="O311" t="str">
         <v/>
@@ -15021,10 +15021,10 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B312" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="C312" t="str">
         <v>Wayward Cave</v>
@@ -15057,10 +15057,10 @@
         <v>No</v>
       </c>
       <c r="M312" t="str">
-        <v/>
+        <v>Seagrass Haven</v>
       </c>
       <c r="N312" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Wayward Cave","count":10}}</v>
       </c>
       <c r="O312" t="str">
         <v/>
@@ -15068,10 +15068,10 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B313" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="C313" t="str">
         <v>Wayward Cave</v>
@@ -15091,8 +15091,8 @@
       <c r="H313" s="1">
         <v>0.2</v>
       </c>
-      <c r="I313" t="str">
-        <v/>
+      <c r="I313" s="1">
+        <v>0.15</v>
       </c>
       <c r="J313" t="str">
         <v>Yes</v>
@@ -15104,10 +15104,10 @@
         <v>No</v>
       </c>
       <c r="M313" t="str">
-        <v/>
+        <v>Seagrass Haven</v>
       </c>
       <c r="N313" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Wayward Cave","count":10}}</v>
       </c>
       <c r="O313" t="str">
         <v/>
@@ -15162,10 +15162,10 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="B315" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="C315" t="str">
         <v>Seagrass Haven</v>
@@ -15198,10 +15198,10 @@
         <v>No</v>
       </c>
       <c r="M315" t="str">
-        <v/>
+        <v>Moonview Arena</v>
       </c>
       <c r="N315" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Seagrass Haven","count":10}}</v>
       </c>
       <c r="O315" t="str">
         <v/>
@@ -15209,10 +15209,10 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="B316" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="C316" t="str">
         <v>Seagrass Haven</v>
@@ -15245,10 +15245,10 @@
         <v>No</v>
       </c>
       <c r="M316" t="str">
-        <v/>
+        <v>Moonview Arena</v>
       </c>
       <c r="N316" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Seagrass Haven","count":10}}</v>
       </c>
       <c r="O316" t="str">
         <v/>
@@ -15256,10 +15256,10 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="B317" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="C317" t="str">
         <v>Seagrass Haven</v>
@@ -15292,10 +15292,10 @@
         <v>No</v>
       </c>
       <c r="M317" t="str">
-        <v/>
+        <v>Moonview Arena</v>
       </c>
       <c r="N317" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Seagrass Haven","count":10}}</v>
       </c>
       <c r="O317" t="str">
         <v/>
@@ -15303,10 +15303,10 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="B318" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="C318" t="str">
         <v>Seagrass Haven</v>
@@ -15339,10 +15339,10 @@
         <v>No</v>
       </c>
       <c r="M318" t="str">
-        <v/>
+        <v>Moonview Arena</v>
       </c>
       <c r="N318" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Seagrass Haven","count":10}}</v>
       </c>
       <c r="O318" t="str">
         <v/>
@@ -15397,7 +15397,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="B320" t="str">
         <v/>
@@ -15444,7 +15444,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="B321" t="str">
         <v/>
@@ -15538,10 +15538,10 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B323" t="str">
-        <v/>
+        <v>Extra Challenge D 1</v>
       </c>
       <c r="C323" t="str">
         <v>Alabaster Icelands Fishing Spot</v>
@@ -15574,10 +15574,10 @@
         <v>No</v>
       </c>
       <c r="M323" t="str">
-        <v/>
+        <v>Worn Bridge</v>
       </c>
       <c r="N323" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Alabaster Icelands Fishing Spot","count":10}}</v>
       </c>
       <c r="O323" t="str">
         <v/>
@@ -15585,10 +15585,10 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B324" t="str">
-        <v/>
+        <v>Extra Challenge D 1</v>
       </c>
       <c r="C324" t="str">
         <v>Alabaster Icelands Fishing Spot</v>
@@ -15621,10 +15621,10 @@
         <v>No</v>
       </c>
       <c r="M324" t="str">
-        <v/>
+        <v>Worn Bridge</v>
       </c>
       <c r="N324" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Alabaster Icelands Fishing Spot","count":10}}</v>
       </c>
       <c r="O324" t="str">
         <v/>
@@ -15679,10 +15679,10 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v/>
+        <v>Extra Challenge D 1</v>
       </c>
       <c r="B326" t="str">
-        <v/>
+        <v>Extra Challenge D 2</v>
       </c>
       <c r="C326" t="str">
         <v>Worn Bridge</v>
@@ -15715,10 +15715,10 @@
         <v>No</v>
       </c>
       <c r="M326" t="str">
-        <v/>
+        <v>Incarnate Fields</v>
       </c>
       <c r="N326" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Worn Bridge","count":10}}</v>
       </c>
       <c r="O326" t="str">
         <v/>
@@ -15773,7 +15773,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v/>
+        <v>Extra Challenge D 2</v>
       </c>
       <c r="B328" t="str">
         <v/>
@@ -15820,7 +15820,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v/>
+        <v>Extra Challenge D 2</v>
       </c>
       <c r="B329" t="str">
         <v/>
@@ -15867,7 +15867,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v/>
+        <v>Extra Challenge D 2</v>
       </c>
       <c r="B330" t="str">
         <v/>
@@ -15961,10 +15961,10 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B332" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="C332" t="str">
         <v>Lake Verity</v>
@@ -15997,10 +15997,10 @@
         <v>No</v>
       </c>
       <c r="M332" t="str">
-        <v/>
+        <v>Lake Valor</v>
       </c>
       <c r="N332" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Lake Verity","count":10}}</v>
       </c>
       <c r="O332" t="str">
         <v/>
@@ -16008,10 +16008,10 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B333" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="C333" t="str">
         <v>Lake Verity</v>
@@ -16044,10 +16044,10 @@
         <v>No</v>
       </c>
       <c r="M333" t="str">
-        <v/>
+        <v>Lake Valor</v>
       </c>
       <c r="N333" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Lake Verity","count":10}}</v>
       </c>
       <c r="O333" t="str">
         <v/>
@@ -16055,10 +16055,10 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B334" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="C334" t="str">
         <v>Lake Verity</v>
@@ -16091,10 +16091,10 @@
         <v>No</v>
       </c>
       <c r="M334" t="str">
-        <v/>
+        <v>Lake Valor</v>
       </c>
       <c r="N334" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Lake Verity","count":10}}</v>
       </c>
       <c r="O334" t="str">
         <v/>
@@ -16149,10 +16149,10 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="B336" t="str">
-        <v/>
+        <v>Extra Challenge E 2</v>
       </c>
       <c r="C336" t="str">
         <v>Lake Valor</v>
@@ -16185,10 +16185,10 @@
         <v>No</v>
       </c>
       <c r="M336" t="str">
-        <v/>
+        <v>Lake of Trials</v>
       </c>
       <c r="N336" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Lake Valor","count":10}}</v>
       </c>
       <c r="O336" t="str">
         <v/>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="B337" t="str">
-        <v/>
+        <v>Extra Challenge E 2</v>
       </c>
       <c r="C337" t="str">
         <v>Lake Valor</v>
@@ -16232,10 +16232,10 @@
         <v>No</v>
       </c>
       <c r="M337" t="str">
-        <v/>
+        <v>Lake of Trials</v>
       </c>
       <c r="N337" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Lake Valor","count":10}}</v>
       </c>
       <c r="O337" t="str">
         <v/>
@@ -16243,10 +16243,10 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="B338" t="str">
-        <v/>
+        <v>Extra Challenge E 2</v>
       </c>
       <c r="C338" t="str">
         <v>Lake Valor</v>
@@ -16279,10 +16279,10 @@
         <v>No</v>
       </c>
       <c r="M338" t="str">
-        <v/>
+        <v>Lake of Trials</v>
       </c>
       <c r="N338" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Lake Valor","count":10}}</v>
       </c>
       <c r="O338" t="str">
         <v/>
@@ -16337,7 +16337,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v/>
+        <v>Extra Challenge E 2</v>
       </c>
       <c r="B340" t="str">
         <v/>
@@ -16384,7 +16384,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v/>
+        <v>Extra Challenge E 2</v>
       </c>
       <c r="B341" t="str">
         <v/>
@@ -16478,10 +16478,10 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B343" t="str">
-        <v/>
+        <v>Extra Challenge F 1</v>
       </c>
       <c r="C343" t="str">
         <v>Etertime Storm</v>
@@ -16514,10 +16514,10 @@
         <v>No</v>
       </c>
       <c r="M343" t="str">
-        <v/>
+        <v>Gym of Etertime</v>
       </c>
       <c r="N343" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Etertime Storm","count":10}}</v>
       </c>
       <c r="O343" t="str">
         <v/>
@@ -16525,10 +16525,10 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B344" t="str">
-        <v/>
+        <v>Extra Challenge F 1</v>
       </c>
       <c r="C344" t="str">
         <v>Etertime Storm</v>
@@ -16561,10 +16561,10 @@
         <v>No</v>
       </c>
       <c r="M344" t="str">
-        <v/>
+        <v>Gym of Etertime</v>
       </c>
       <c r="N344" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Etertime Storm","count":10}}</v>
       </c>
       <c r="O344" t="str">
         <v/>
@@ -16572,10 +16572,10 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B345" t="str">
-        <v/>
+        <v>Extra Challenge F 1</v>
       </c>
       <c r="C345" t="str">
         <v>Etertime Storm</v>
@@ -16608,10 +16608,10 @@
         <v>No</v>
       </c>
       <c r="M345" t="str">
-        <v/>
+        <v>Gym of Etertime</v>
       </c>
       <c r="N345" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Etertime Storm","count":10}}</v>
       </c>
       <c r="O345" t="str">
         <v/>
@@ -16619,10 +16619,10 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B346" t="str">
-        <v/>
+        <v>Extra Challenge F 1</v>
       </c>
       <c r="C346" t="str">
         <v>Etertime Storm</v>
@@ -16655,10 +16655,10 @@
         <v>No</v>
       </c>
       <c r="M346" t="str">
-        <v/>
+        <v>Gym of Etertime</v>
       </c>
       <c r="N346" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"routeName":"Etertime Storm","count":10}}</v>
       </c>
       <c r="O346" t="str">
         <v/>
@@ -16760,10 +16760,10 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v/>
+        <v>Key to Etertime Citadel</v>
       </c>
       <c r="B349" t="str">
-        <v/>
+        <v>Etertime Citadel</v>
       </c>
       <c r="C349" t="str">
         <v>Etertime Citadel</v>
@@ -16799,7 +16799,7 @@
         <v/>
       </c>
       <c r="N349" t="str">
-        <v/>
+        <v>{"catchSpecies":["Arceus","Dialga","Palkia","Giratina"]}</v>
       </c>
       <c r="O349" t="str">
         <v/>
@@ -16807,10 +16807,10 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v/>
+        <v>Key to Etertime Citadel</v>
       </c>
       <c r="B350" t="str">
-        <v/>
+        <v>Etertime Citadel</v>
       </c>
       <c r="C350" t="str">
         <v>Etertime Citadel</v>
@@ -16846,7 +16846,7 @@
         <v/>
       </c>
       <c r="N350" t="str">
-        <v/>
+        <v>{"catchSpecies":["Arceus","Dialga","Palkia","Giratina"]}</v>
       </c>
       <c r="O350" t="str">
         <v/>
@@ -16854,10 +16854,10 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v/>
+        <v>Key to Etertime Citadel</v>
       </c>
       <c r="B351" t="str">
-        <v/>
+        <v>Etertime Citadel</v>
       </c>
       <c r="C351" t="str">
         <v>Etertime Citadel</v>
@@ -16893,22 +16893,304 @@
         <v/>
       </c>
       <c r="N351" t="str">
-        <v/>
+        <v>{"catchSpecies":["Arceus","Dialga","Palkia","Giratina"]}</v>
       </c>
       <c r="O351" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v/>
+      </c>
+      <c r="B352" t="str">
+        <v>Extra Challenge B 4</v>
+      </c>
+      <c r="C352" t="str">
+        <v>Extra Challenge B 4</v>
+      </c>
+      <c r="D352" t="str">
+        <v/>
+      </c>
+      <c r="E352" t="str">
+        <v/>
+      </c>
+      <c r="F352" t="str">
+        <v/>
+      </c>
+      <c r="G352" t="str">
+        <v/>
+      </c>
+      <c r="H352" t="str">
+        <v/>
+      </c>
+      <c r="I352" t="str">
+        <v/>
+      </c>
+      <c r="J352" t="str">
+        <v/>
+      </c>
+      <c r="K352" t="str">
+        <v/>
+      </c>
+      <c r="L352" t="str">
+        <v>No</v>
+      </c>
+      <c r="M352" t="str">
+        <v/>
+      </c>
+      <c r="N352" t="str">
+        <v>{"catchSpecies":["Kleavor","Arcanine","Lilligant","Electrode","Avalugg"]}</v>
+      </c>
+      <c r="O352" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v/>
+      </c>
+      <c r="B353" t="str">
+        <v>Extra Challenge C 3</v>
+      </c>
+      <c r="C353" t="str">
+        <v>Extra Challenge C 3</v>
+      </c>
+      <c r="D353" t="str">
+        <v/>
+      </c>
+      <c r="E353" t="str">
+        <v/>
+      </c>
+      <c r="F353" t="str">
+        <v/>
+      </c>
+      <c r="G353" t="str">
+        <v/>
+      </c>
+      <c r="H353" t="str">
+        <v/>
+      </c>
+      <c r="I353" t="str">
+        <v/>
+      </c>
+      <c r="J353" t="str">
+        <v/>
+      </c>
+      <c r="K353" t="str">
+        <v/>
+      </c>
+      <c r="L353" t="str">
+        <v>No</v>
+      </c>
+      <c r="M353" t="str">
+        <v/>
+      </c>
+      <c r="N353" t="str">
+        <v>{"catchSpecies":["Darkrai","Shaymin","Cresselia"]}</v>
+      </c>
+      <c r="O353" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v/>
+      </c>
+      <c r="B354" t="str">
+        <v>Extra Challenge D 3</v>
+      </c>
+      <c r="C354" t="str">
+        <v>Extra Challenge D 3</v>
+      </c>
+      <c r="D354" t="str">
+        <v/>
+      </c>
+      <c r="E354" t="str">
+        <v/>
+      </c>
+      <c r="F354" t="str">
+        <v/>
+      </c>
+      <c r="G354" t="str">
+        <v/>
+      </c>
+      <c r="H354" t="str">
+        <v/>
+      </c>
+      <c r="I354" t="str">
+        <v/>
+      </c>
+      <c r="J354" t="str">
+        <v/>
+      </c>
+      <c r="K354" t="str">
+        <v/>
+      </c>
+      <c r="L354" t="str">
+        <v>No</v>
+      </c>
+      <c r="M354" t="str">
+        <v/>
+      </c>
+      <c r="N354" t="str">
+        <v>{"catchSpecies":["Tornadus","Thundurus","Landorus","Enamorus"]}</v>
+      </c>
+      <c r="O354" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v/>
+      </c>
+      <c r="B355" t="str">
+        <v>Extra Challenge E 3</v>
+      </c>
+      <c r="C355" t="str">
+        <v>Extra Challenge E 3</v>
+      </c>
+      <c r="D355" t="str">
+        <v/>
+      </c>
+      <c r="E355" t="str">
+        <v/>
+      </c>
+      <c r="F355" t="str">
+        <v/>
+      </c>
+      <c r="G355" t="str">
+        <v/>
+      </c>
+      <c r="H355" t="str">
+        <v/>
+      </c>
+      <c r="I355" t="str">
+        <v/>
+      </c>
+      <c r="J355" t="str">
+        <v/>
+      </c>
+      <c r="K355" t="str">
+        <v/>
+      </c>
+      <c r="L355" t="str">
+        <v>No</v>
+      </c>
+      <c r="M355" t="str">
+        <v/>
+      </c>
+      <c r="N355" t="str">
+        <v>{"catchSpecies":["Uxie","Mesprit","Azelf"]}</v>
+      </c>
+      <c r="O355" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v/>
+      </c>
+      <c r="B356" t="str">
+        <v>Extra Challenge F 2</v>
+      </c>
+      <c r="C356" t="str">
+        <v>Extra Challenge F 2</v>
+      </c>
+      <c r="D356" t="str">
+        <v/>
+      </c>
+      <c r="E356" t="str">
+        <v/>
+      </c>
+      <c r="F356" t="str">
+        <v/>
+      </c>
+      <c r="G356" t="str">
+        <v/>
+      </c>
+      <c r="H356" t="str">
+        <v/>
+      </c>
+      <c r="I356" t="str">
+        <v/>
+      </c>
+      <c r="J356" t="str">
+        <v/>
+      </c>
+      <c r="K356" t="str">
+        <v/>
+      </c>
+      <c r="L356" t="str">
+        <v>No</v>
+      </c>
+      <c r="M356" t="str">
+        <v/>
+      </c>
+      <c r="N356" t="str">
+        <v>{"defeatMultipleSpecific":[{"name":"Adam"},{"name":"Irida"}]}</v>
+      </c>
+      <c r="O356" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v/>
+      </c>
+      <c r="B357" t="str">
+        <v>Key to Etertime Citadel</v>
+      </c>
+      <c r="C357" t="str">
+        <v>Key to Etertime Citadel</v>
+      </c>
+      <c r="D357" t="str">
+        <v/>
+      </c>
+      <c r="E357" t="str">
+        <v/>
+      </c>
+      <c r="F357" t="str">
+        <v/>
+      </c>
+      <c r="G357" t="str">
+        <v/>
+      </c>
+      <c r="H357" t="str">
+        <v/>
+      </c>
+      <c r="I357" t="str">
+        <v/>
+      </c>
+      <c r="J357" t="str">
+        <v/>
+      </c>
+      <c r="K357" t="str">
+        <v/>
+      </c>
+      <c r="L357" t="str">
+        <v>No</v>
+      </c>
+      <c r="M357" t="str">
+        <v>Etertime Citadel</v>
+      </c>
+      <c r="N357" t="str">
+        <v>{"completeChallenges":["Extra Challenge C 3","Extra Challenge D 3","Extra Challenge E 3","Extra Challenge F 2"]}</v>
+      </c>
+      <c r="O357" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O351"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O357"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F72"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -18230,9 +18512,129 @@
         <v/>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Extra Challenge B 4</v>
+      </c>
+      <c r="B67" t="str">
+        <v>{"catchSpecies":["Kleavor","Arcanine","Lilligant","Electrode","Avalugg"]}</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Extra Challenge C 3</v>
+      </c>
+      <c r="B68" t="str">
+        <v>{"catchSpecies":["Darkrai","Shaymin","Cresselia"]}</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Extra Challenge D 3</v>
+      </c>
+      <c r="B69" t="str">
+        <v>{"catchSpecies":["Tornadus","Thundurus","Landorus","Enamorus"]}</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Extra Challenge E 3</v>
+      </c>
+      <c r="B70" t="str">
+        <v>{"catchSpecies":["Uxie","Mesprit","Azelf"]}</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Extra Challenge F 2</v>
+      </c>
+      <c r="B71" t="str">
+        <v>{"defeatMultipleSpecific":[{"name":"Adam"},{"name":"Irida"}]}</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Key to Etertime Citadel</v>
+      </c>
+      <c r="B72" t="str">
+        <v>{"completeChallenges":["Extra Challenge C 3","Extra Challenge D 3","Extra Challenge E 3","Extra Challenge F 2"]}</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Etertime Citadel</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F72"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/9_Hisui_Data.xlsx
+++ b/9_Hisui_Data.xlsx
@@ -14710,7 +14710,7 @@
         <v>90-92</v>
       </c>
       <c r="G305" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H305" s="1">
         <v>0.25</v>
@@ -14757,7 +14757,7 @@
         <v>90-92</v>
       </c>
       <c r="G306" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H306" s="1">
         <v>0.25</v>
@@ -14804,7 +14804,7 @@
         <v>90-92</v>
       </c>
       <c r="G307" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H307" s="1">
         <v>0.25</v>
@@ -14851,7 +14851,7 @@
         <v>90-92</v>
       </c>
       <c r="G308" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H308" s="1">
         <v>0.25</v>
